--- a/chamba/Excel_Practice/134 - Calculations with named ranges.xlsx
+++ b/chamba/Excel_Practice/134 - Calculations with named ranges.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\studio750\Documents\Data Wrangling MOOC\Course1\Week3\Workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex_\Em1Repo\chamba\Excel_Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27302FF-A9D7-4560-A07E-B1A0247F2108}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5205ED63-D34D-4E50-9678-DA39289BD690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-4185" windowWidth="28996" windowHeight="16395" activeTab="1" xr2:uid="{EC2FC403-3BD3-48C3-93CE-3A4A505B5772}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{EC2FC403-3BD3-48C3-93CE-3A4A505B5772}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplier Invoice Statement" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <definedName name="Amount_Paid">'MC Invoice Report'!$J$5:$J$88</definedName>
     <definedName name="Bank_Details">'MC Invoice Report'!$G$5:$G$88</definedName>
     <definedName name="Due_Date">'MC Invoice Report'!$E$5:$E$88</definedName>
+    <definedName name="flat_rate">2</definedName>
     <definedName name="Invoice_Date">'MC Invoice Report'!$D$5:$D$88</definedName>
     <definedName name="Invoice_Day">'MC Invoice Report'!$L$5:$L$88</definedName>
     <definedName name="Invoice_Month">'MC Invoice Report'!$K$5:$K$88</definedName>
@@ -1422,7 +1423,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
@@ -1433,7 +1434,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1459,13 +1459,7 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="4" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1474,17 +1468,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="11"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -1522,9 +1509,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1562,7 +1549,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1668,7 +1655,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1810,7 +1797,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1820,107 +1807,107 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB52FEA-723B-4838-99B7-4396BFB5D3CB}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:V85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="5.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="5.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.5546875" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" customWidth="1"/>
+    <col min="15" max="15" width="11.109375" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="11.85546875" style="8" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" style="24" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11.88671875" customWidth="1"/>
+    <col min="19" max="19" width="11.88671875" style="7" customWidth="1"/>
+    <col min="22" max="22" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="7" customFormat="1" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:22" s="7" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="Q1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="U1" s="18" t="s">
+      <c r="U1" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="V1" s="19">
+      <c r="V1" s="18">
         <f>SUM(Q2:Q85)</f>
         <v>48282.62999999999</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>24673</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="21" t="s">
         <v>358</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1969,27 +1956,27 @@
         <f>VALUE(SUBSTITUTE(SUBSTITUTE(F2,"S","$"),CHAR(160),""))</f>
         <v>742.5</v>
       </c>
-      <c r="R2" s="20">
+      <c r="R2" s="19">
         <f>DATE(2020,MONTH(1&amp;M2),RIGHT(D2,2))</f>
         <v>43892</v>
       </c>
-      <c r="S2" s="20">
+      <c r="S2" s="19">
         <f>DATE(2020,4,RIGHT(C2,2))</f>
         <v>43938</v>
       </c>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>24673</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -2038,26 +2025,26 @@
         <f t="shared" ref="Q3:Q66" si="6">VALUE(SUBSTITUTE(SUBSTITUTE(F3,"S","$"),CHAR(160),""))</f>
         <v>1021.02</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="19">
         <f t="shared" ref="R3:R66" si="7">DATE(2020,MONTH(1&amp;M3),RIGHT(D3,2))</f>
         <v>43922</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="19">
         <f t="shared" ref="S3:S66" si="8">DATE(2020,4,RIGHT(C3,2))</f>
         <v>43941</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>24675</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="21" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -2106,26 +2093,26 @@
         <f t="shared" si="6"/>
         <v>409.53</v>
       </c>
-      <c r="R4" s="20">
+      <c r="R4" s="19">
         <f t="shared" si="7"/>
         <v>43906</v>
       </c>
-      <c r="S4" s="20">
+      <c r="S4" s="19">
         <f t="shared" si="8"/>
         <v>43926</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>24676</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>67</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -2174,26 +2161,26 @@
         <f t="shared" si="6"/>
         <v>234.96</v>
       </c>
-      <c r="R5" s="20">
+      <c r="R5" s="19">
         <f t="shared" si="7"/>
         <v>43915</v>
       </c>
-      <c r="S5" s="20">
+      <c r="S5" s="19">
         <f t="shared" si="8"/>
         <v>43941</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>24677</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -2242,26 +2229,26 @@
         <f t="shared" si="6"/>
         <v>450.12</v>
       </c>
-      <c r="R6" s="20">
+      <c r="R6" s="19">
         <f t="shared" si="7"/>
         <v>43907</v>
       </c>
-      <c r="S6" s="20">
+      <c r="S6" s="19">
         <f t="shared" si="8"/>
         <v>43931</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>24679</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -2310,26 +2297,26 @@
         <f t="shared" si="6"/>
         <v>114.18</v>
       </c>
-      <c r="R7" s="20">
+      <c r="R7" s="19">
         <f t="shared" si="7"/>
         <v>43930</v>
       </c>
-      <c r="S7" s="20">
+      <c r="S7" s="19">
         <f t="shared" si="8"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>24679</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>71</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -2378,26 +2365,26 @@
         <f t="shared" si="6"/>
         <v>930.93</v>
       </c>
-      <c r="R8" s="20">
+      <c r="R8" s="19">
         <f t="shared" si="7"/>
         <v>43913</v>
       </c>
-      <c r="S8" s="20">
+      <c r="S8" s="19">
         <f t="shared" si="8"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>24680</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="21" t="s">
         <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2446,26 +2433,26 @@
         <f t="shared" si="6"/>
         <v>466.29</v>
       </c>
-      <c r="R9" s="20">
+      <c r="R9" s="19">
         <f t="shared" si="7"/>
         <v>43917</v>
       </c>
-      <c r="S9" s="20">
+      <c r="S9" s="19">
         <f t="shared" si="8"/>
         <v>43935</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>24683</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="21" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -2514,26 +2501,26 @@
         <f t="shared" si="6"/>
         <v>222.42</v>
       </c>
-      <c r="R10" s="20">
+      <c r="R10" s="19">
         <f t="shared" si="7"/>
         <v>43912</v>
       </c>
-      <c r="S10" s="20">
+      <c r="S10" s="19">
         <f t="shared" si="8"/>
         <v>43948</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>24685</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="21" t="s">
         <v>92</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -2582,26 +2569,26 @@
         <f t="shared" si="6"/>
         <v>679.8</v>
       </c>
-      <c r="R11" s="20">
+      <c r="R11" s="19">
         <f t="shared" si="7"/>
         <v>43899</v>
       </c>
-      <c r="S11" s="20">
+      <c r="S11" s="19">
         <f t="shared" si="8"/>
         <v>43932</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>24690</v>
       </c>
       <c r="B12" s="2">
         <v>1</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="21" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -2650,26 +2637,26 @@
         <f t="shared" si="6"/>
         <v>171.93</v>
       </c>
-      <c r="R12" s="20">
+      <c r="R12" s="19">
         <f t="shared" si="7"/>
         <v>43925</v>
       </c>
-      <c r="S12" s="20">
+      <c r="S12" s="19">
         <f t="shared" si="8"/>
         <v>43944</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>24693</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="21" t="s">
         <v>97</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -2718,26 +2705,26 @@
         <f t="shared" si="6"/>
         <v>623.70000000000005</v>
       </c>
-      <c r="R13" s="20">
+      <c r="R13" s="19">
         <f t="shared" si="7"/>
         <v>43885</v>
       </c>
-      <c r="S13" s="20">
+      <c r="S13" s="19">
         <f t="shared" si="8"/>
         <v>43927</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>24697</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="21" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -2786,26 +2773,26 @@
         <f t="shared" si="6"/>
         <v>221.1</v>
       </c>
-      <c r="R14" s="20">
+      <c r="R14" s="19">
         <f t="shared" si="7"/>
         <v>43919</v>
       </c>
-      <c r="S14" s="20">
+      <c r="S14" s="19">
         <f t="shared" si="8"/>
         <v>43945</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>24698</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="21" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -2854,26 +2841,26 @@
         <f t="shared" si="6"/>
         <v>393.36</v>
       </c>
-      <c r="R15" s="20">
+      <c r="R15" s="19">
         <f t="shared" si="7"/>
         <v>43930</v>
       </c>
-      <c r="S15" s="20">
+      <c r="S15" s="19">
         <f t="shared" si="8"/>
         <v>43949</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>24699</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="21" t="s">
         <v>92</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -2922,26 +2909,26 @@
         <f t="shared" si="6"/>
         <v>642.17999999999995</v>
       </c>
-      <c r="R16" s="20">
+      <c r="R16" s="19">
         <f t="shared" si="7"/>
         <v>43899</v>
       </c>
-      <c r="S16" s="20">
+      <c r="S16" s="19">
         <f t="shared" si="8"/>
         <v>43942</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>24704</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="21" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -2990,26 +2977,26 @@
         <f t="shared" si="6"/>
         <v>499.95</v>
       </c>
-      <c r="R17" s="20">
+      <c r="R17" s="19">
         <f t="shared" si="7"/>
         <v>43909</v>
       </c>
-      <c r="S17" s="20">
+      <c r="S17" s="19">
         <f t="shared" si="8"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>24707</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="21" t="s">
         <v>108</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -3058,26 +3045,26 @@
         <f t="shared" si="6"/>
         <v>299.64</v>
       </c>
-      <c r="R18" s="20">
+      <c r="R18" s="19">
         <f t="shared" si="7"/>
         <v>43890</v>
       </c>
-      <c r="S18" s="20">
+      <c r="S18" s="19">
         <f t="shared" si="8"/>
         <v>43928</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>24712</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="21" t="s">
         <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -3126,26 +3113,26 @@
         <f t="shared" si="6"/>
         <v>312.83999999999997</v>
       </c>
-      <c r="R19" s="20">
+      <c r="R19" s="19">
         <f t="shared" si="7"/>
         <v>43912</v>
       </c>
-      <c r="S19" s="20">
+      <c r="S19" s="19">
         <f t="shared" si="8"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>24717</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="21" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -3194,26 +3181,26 @@
         <f t="shared" si="6"/>
         <v>993.63</v>
       </c>
-      <c r="R20" s="20">
+      <c r="R20" s="19">
         <f t="shared" si="7"/>
         <v>43904</v>
       </c>
-      <c r="S20" s="20">
+      <c r="S20" s="19">
         <f t="shared" si="8"/>
         <v>43926</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>24722</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="21" t="s">
         <v>69</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -3262,26 +3249,26 @@
         <f t="shared" si="6"/>
         <v>1053.69</v>
       </c>
-      <c r="R21" s="20">
+      <c r="R21" s="19">
         <f t="shared" si="7"/>
         <v>43917</v>
       </c>
-      <c r="S21" s="20">
+      <c r="S21" s="19">
         <f t="shared" si="8"/>
         <v>43922</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>24727</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="21" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -3330,26 +3317,26 @@
         <f t="shared" si="6"/>
         <v>1047.75</v>
       </c>
-      <c r="R22" s="20">
+      <c r="R22" s="19">
         <f t="shared" si="7"/>
         <v>43929</v>
       </c>
-      <c r="S22" s="20">
+      <c r="S22" s="19">
         <f t="shared" si="8"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>24730</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="21" t="s">
         <v>119</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -3398,26 +3385,26 @@
         <f t="shared" si="6"/>
         <v>1096.92</v>
       </c>
-      <c r="R23" s="20">
+      <c r="R23" s="19">
         <f t="shared" si="7"/>
         <v>43888</v>
       </c>
-      <c r="S23" s="20">
+      <c r="S23" s="19">
         <f t="shared" si="8"/>
         <v>43929</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>24732</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="21" t="s">
         <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -3466,26 +3453,26 @@
         <f t="shared" si="6"/>
         <v>257.07</v>
       </c>
-      <c r="R24" s="20">
+      <c r="R24" s="19">
         <f t="shared" si="7"/>
         <v>43886</v>
       </c>
-      <c r="S24" s="20">
+      <c r="S24" s="19">
         <f t="shared" si="8"/>
         <v>43928</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24735</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="21" t="s">
         <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -3534,26 +3521,26 @@
         <f t="shared" si="6"/>
         <v>215.49</v>
       </c>
-      <c r="R25" s="20">
+      <c r="R25" s="19">
         <f t="shared" si="7"/>
         <v>43945</v>
       </c>
-      <c r="S25" s="20">
+      <c r="S25" s="19">
         <f t="shared" si="8"/>
         <v>43949</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24739</v>
       </c>
       <c r="B26" s="2">
         <v>1</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -3602,26 +3589,26 @@
         <f t="shared" si="6"/>
         <v>455.07</v>
       </c>
-      <c r="R26" s="20">
+      <c r="R26" s="19">
         <f t="shared" si="7"/>
         <v>43926</v>
       </c>
-      <c r="S26" s="20">
+      <c r="S26" s="19">
         <f t="shared" si="8"/>
         <v>43945</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>24740</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -3670,26 +3657,26 @@
         <f t="shared" si="6"/>
         <v>711.81</v>
       </c>
-      <c r="R27" s="20">
+      <c r="R27" s="19">
         <f t="shared" si="7"/>
         <v>43923</v>
       </c>
-      <c r="S27" s="20">
+      <c r="S27" s="19">
         <f t="shared" si="8"/>
         <v>43930</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>24743</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="21" t="s">
         <v>130</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -3738,26 +3725,26 @@
         <f t="shared" si="6"/>
         <v>78.540000000000006</v>
       </c>
-      <c r="R28" s="20">
+      <c r="R28" s="19">
         <f t="shared" si="7"/>
         <v>43911</v>
       </c>
-      <c r="S28" s="20">
+      <c r="S28" s="19">
         <f t="shared" si="8"/>
         <v>43925</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>24746</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -3806,26 +3793,26 @@
         <f t="shared" si="6"/>
         <v>302.61</v>
       </c>
-      <c r="R29" s="20">
+      <c r="R29" s="19">
         <f t="shared" si="7"/>
         <v>43892</v>
       </c>
-      <c r="S29" s="20">
+      <c r="S29" s="19">
         <f t="shared" si="8"/>
         <v>43927</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>24750</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="21" t="s">
         <v>65</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -3874,26 +3861,26 @@
         <f t="shared" si="6"/>
         <v>426.03</v>
       </c>
-      <c r="R30" s="20">
+      <c r="R30" s="19">
         <f t="shared" si="7"/>
         <v>43886</v>
       </c>
-      <c r="S30" s="20">
+      <c r="S30" s="19">
         <f t="shared" si="8"/>
         <v>43931</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>24753</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="21" t="s">
         <v>92</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -3942,26 +3929,26 @@
         <f t="shared" si="6"/>
         <v>489.72</v>
       </c>
-      <c r="R31" s="20">
+      <c r="R31" s="19">
         <f t="shared" si="7"/>
         <v>43899</v>
       </c>
-      <c r="S31" s="20">
+      <c r="S31" s="19">
         <f t="shared" si="8"/>
         <v>43932</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>24754</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="21" t="s">
         <v>67</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -4010,26 +3997,26 @@
         <f t="shared" si="6"/>
         <v>352.44</v>
       </c>
-      <c r="R32" s="20">
+      <c r="R32" s="19">
         <f t="shared" si="7"/>
         <v>43915</v>
       </c>
-      <c r="S32" s="20">
+      <c r="S32" s="19">
         <f t="shared" si="8"/>
         <v>43949</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>24756</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="21" t="s">
         <v>39</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -4078,26 +4065,26 @@
         <f t="shared" si="6"/>
         <v>238.59</v>
       </c>
-      <c r="R33" s="20">
+      <c r="R33" s="19">
         <f t="shared" si="7"/>
         <v>43912</v>
       </c>
-      <c r="S33" s="20">
+      <c r="S33" s="19">
         <f t="shared" si="8"/>
         <v>43937</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>24757</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -4146,26 +4133,26 @@
         <f t="shared" si="6"/>
         <v>549.12</v>
       </c>
-      <c r="R34" s="20">
+      <c r="R34" s="19">
         <f t="shared" si="7"/>
         <v>43936</v>
       </c>
-      <c r="S34" s="20">
+      <c r="S34" s="19">
         <f t="shared" si="8"/>
         <v>43941</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>24758</v>
       </c>
       <c r="B35" s="2">
         <v>1</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="21" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -4214,26 +4201,26 @@
         <f t="shared" si="6"/>
         <v>322.41000000000003</v>
       </c>
-      <c r="R35" s="20">
+      <c r="R35" s="19">
         <f t="shared" si="7"/>
         <v>43893</v>
       </c>
-      <c r="S35" s="20">
+      <c r="S35" s="19">
         <f t="shared" si="8"/>
         <v>43923</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>24759</v>
       </c>
       <c r="B36" s="2">
         <v>1</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -4282,26 +4269,26 @@
         <f t="shared" si="6"/>
         <v>644.82000000000005</v>
       </c>
-      <c r="R36" s="20">
+      <c r="R36" s="19">
         <f t="shared" si="7"/>
         <v>43892</v>
       </c>
-      <c r="S36" s="20">
+      <c r="S36" s="19">
         <f t="shared" si="8"/>
         <v>43934</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>24760</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -4350,26 +4337,26 @@
         <f t="shared" si="6"/>
         <v>113.19</v>
       </c>
-      <c r="R37" s="20">
+      <c r="R37" s="19">
         <f t="shared" si="7"/>
         <v>43923</v>
       </c>
-      <c r="S37" s="20">
+      <c r="S37" s="19">
         <f t="shared" si="8"/>
         <v>43944</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>24761</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="21" t="s">
         <v>22</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -4418,26 +4405,26 @@
         <f t="shared" si="6"/>
         <v>449.13</v>
       </c>
-      <c r="R38" s="20">
+      <c r="R38" s="19">
         <f t="shared" si="7"/>
         <v>43941</v>
       </c>
-      <c r="S38" s="20">
+      <c r="S38" s="19">
         <f t="shared" si="8"/>
         <v>43949</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>24764</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="21" t="s">
         <v>130</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -4486,26 +4473,26 @@
         <f t="shared" si="6"/>
         <v>819.06</v>
       </c>
-      <c r="R39" s="20">
+      <c r="R39" s="19">
         <f t="shared" si="7"/>
         <v>43911</v>
       </c>
-      <c r="S39" s="20">
+      <c r="S39" s="19">
         <f t="shared" si="8"/>
         <v>43933</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>24767</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="23" t="s">
+      <c r="D40" s="21" t="s">
         <v>155</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -4554,26 +4541,26 @@
         <f t="shared" si="6"/>
         <v>1019.04</v>
       </c>
-      <c r="R40" s="20">
+      <c r="R40" s="19">
         <f t="shared" si="7"/>
         <v>43880</v>
       </c>
-      <c r="S40" s="20">
+      <c r="S40" s="19">
         <f t="shared" si="8"/>
         <v>43924</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>24771</v>
       </c>
       <c r="B41" s="2">
         <v>1</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D41" s="21" t="s">
         <v>47</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -4622,26 +4609,26 @@
         <f t="shared" si="6"/>
         <v>736.23</v>
       </c>
-      <c r="R41" s="20">
+      <c r="R41" s="19">
         <f t="shared" si="7"/>
         <v>43919</v>
       </c>
-      <c r="S41" s="20">
+      <c r="S41" s="19">
         <f t="shared" si="8"/>
         <v>43935</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>24775</v>
       </c>
       <c r="B42" s="2">
         <v>1</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -4690,26 +4677,26 @@
         <f t="shared" si="6"/>
         <v>600.27</v>
       </c>
-      <c r="R42" s="20">
+      <c r="R42" s="19">
         <f t="shared" si="7"/>
         <v>43895</v>
       </c>
-      <c r="S42" s="20">
+      <c r="S42" s="19">
         <f t="shared" si="8"/>
         <v>43937</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>24779</v>
       </c>
       <c r="B43" s="2">
         <v>1</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -4758,26 +4745,26 @@
         <f t="shared" si="6"/>
         <v>480.81</v>
       </c>
-      <c r="R43" s="20">
+      <c r="R43" s="19">
         <f t="shared" si="7"/>
         <v>43907</v>
       </c>
-      <c r="S43" s="20">
+      <c r="S43" s="19">
         <f t="shared" si="8"/>
         <v>43929</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>24784</v>
       </c>
       <c r="B44" s="2">
         <v>1</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="23" t="s">
+      <c r="D44" s="21" t="s">
         <v>165</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -4826,26 +4813,26 @@
         <f t="shared" si="6"/>
         <v>253.77</v>
       </c>
-      <c r="R44" s="20">
+      <c r="R44" s="19">
         <f t="shared" si="7"/>
         <v>43908</v>
       </c>
-      <c r="S44" s="20">
+      <c r="S44" s="19">
         <f t="shared" si="8"/>
         <v>43948</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>24788</v>
       </c>
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="21" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -4894,26 +4881,26 @@
         <f t="shared" si="6"/>
         <v>442.86</v>
       </c>
-      <c r="R45" s="20">
+      <c r="R45" s="19">
         <f t="shared" si="7"/>
         <v>43906</v>
       </c>
-      <c r="S45" s="20">
+      <c r="S45" s="19">
         <f t="shared" si="8"/>
         <v>43949</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>24792</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="21" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -4962,26 +4949,26 @@
         <f t="shared" si="6"/>
         <v>630.96</v>
       </c>
-      <c r="R46" s="20">
+      <c r="R46" s="19">
         <f t="shared" si="7"/>
         <v>43901</v>
       </c>
-      <c r="S46" s="20">
+      <c r="S46" s="19">
         <f t="shared" si="8"/>
         <v>43924</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>24793</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E47" s="2" t="s">
@@ -5030,26 +5017,26 @@
         <f t="shared" si="6"/>
         <v>821.37</v>
       </c>
-      <c r="R47" s="20">
+      <c r="R47" s="19">
         <f t="shared" si="7"/>
         <v>43895</v>
       </c>
-      <c r="S47" s="20">
+      <c r="S47" s="19">
         <f t="shared" si="8"/>
         <v>43925</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>24795</v>
       </c>
       <c r="B48" s="2">
         <v>1</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="23" t="s">
+      <c r="D48" s="21" t="s">
         <v>119</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -5098,26 +5085,26 @@
         <f t="shared" si="6"/>
         <v>950.73</v>
       </c>
-      <c r="R48" s="20">
+      <c r="R48" s="19">
         <f t="shared" si="7"/>
         <v>43888</v>
       </c>
-      <c r="S48" s="20">
+      <c r="S48" s="19">
         <f t="shared" si="8"/>
         <v>43928</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>24798</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D49" s="23" t="s">
+      <c r="D49" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -5166,26 +5153,26 @@
         <f t="shared" si="6"/>
         <v>956.34</v>
       </c>
-      <c r="R49" s="20">
+      <c r="R49" s="19">
         <f t="shared" si="7"/>
         <v>43921</v>
       </c>
-      <c r="S49" s="20">
+      <c r="S49" s="19">
         <f t="shared" si="8"/>
         <v>43931</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>24801</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="21" t="s">
         <v>69</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -5234,26 +5221,26 @@
         <f t="shared" si="6"/>
         <v>1094.28</v>
       </c>
-      <c r="R50" s="20">
+      <c r="R50" s="19">
         <f t="shared" si="7"/>
         <v>43917</v>
       </c>
-      <c r="S50" s="20">
+      <c r="S50" s="19">
         <f t="shared" si="8"/>
         <v>43933</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>24803</v>
       </c>
       <c r="B51" s="2">
         <v>1</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D51" s="21" t="s">
         <v>165</v>
       </c>
       <c r="E51" s="2" t="s">
@@ -5302,26 +5289,26 @@
         <f t="shared" si="6"/>
         <v>628.98</v>
       </c>
-      <c r="R51" s="20">
+      <c r="R51" s="19">
         <f t="shared" si="7"/>
         <v>43908</v>
       </c>
-      <c r="S51" s="20">
+      <c r="S51" s="19">
         <f t="shared" si="8"/>
         <v>43926</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>24808</v>
       </c>
       <c r="B52" s="2">
         <v>1</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="23" t="s">
+      <c r="D52" s="21" t="s">
         <v>53</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -5370,26 +5357,26 @@
         <f t="shared" si="6"/>
         <v>1058.31</v>
       </c>
-      <c r="R52" s="20">
+      <c r="R52" s="19">
         <f t="shared" si="7"/>
         <v>43929</v>
       </c>
-      <c r="S52" s="20">
+      <c r="S52" s="19">
         <f t="shared" si="8"/>
         <v>43941</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>24813</v>
       </c>
       <c r="B53" s="2">
         <v>1</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -5438,26 +5425,26 @@
         <f t="shared" si="6"/>
         <v>705.54</v>
       </c>
-      <c r="R53" s="20">
+      <c r="R53" s="19">
         <f t="shared" si="7"/>
         <v>43921</v>
       </c>
-      <c r="S53" s="20">
+      <c r="S53" s="19">
         <f t="shared" si="8"/>
         <v>43929</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>24815</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="21" t="s">
         <v>68</v>
       </c>
       <c r="E54" s="2" t="s">
@@ -5506,26 +5493,26 @@
         <f t="shared" si="6"/>
         <v>138.6</v>
       </c>
-      <c r="R54" s="20">
+      <c r="R54" s="19">
         <f t="shared" si="7"/>
         <v>43935</v>
       </c>
-      <c r="S54" s="20">
+      <c r="S54" s="19">
         <f t="shared" si="8"/>
         <v>43948</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>24819</v>
       </c>
       <c r="B55" s="2">
         <v>1</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D55" s="23" t="s">
+      <c r="D55" s="21" t="s">
         <v>61</v>
       </c>
       <c r="E55" s="2" t="s">
@@ -5574,26 +5561,26 @@
         <f t="shared" si="6"/>
         <v>417.12</v>
       </c>
-      <c r="R55" s="20">
+      <c r="R55" s="19">
         <f t="shared" si="7"/>
         <v>43914</v>
       </c>
-      <c r="S55" s="20">
+      <c r="S55" s="19">
         <f t="shared" si="8"/>
         <v>43928</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>24822</v>
       </c>
       <c r="B56" s="2">
         <v>1</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D56" s="23" t="s">
+      <c r="D56" s="21" t="s">
         <v>71</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -5642,26 +5629,26 @@
         <f t="shared" si="6"/>
         <v>422.73</v>
       </c>
-      <c r="R56" s="20">
+      <c r="R56" s="19">
         <f t="shared" si="7"/>
         <v>43913</v>
       </c>
-      <c r="S56" s="20">
+      <c r="S56" s="19">
         <f t="shared" si="8"/>
         <v>43939</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>24824</v>
       </c>
       <c r="B57" s="2">
         <v>1</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="21" t="s">
         <v>165</v>
       </c>
       <c r="E57" s="2" t="s">
@@ -5710,26 +5697,26 @@
         <f t="shared" si="6"/>
         <v>1061.94</v>
       </c>
-      <c r="R57" s="20">
+      <c r="R57" s="19">
         <f t="shared" si="7"/>
         <v>43908</v>
       </c>
-      <c r="S57" s="20">
+      <c r="S57" s="19">
         <f t="shared" si="8"/>
         <v>43935</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>24825</v>
       </c>
       <c r="B58" s="2">
         <v>1</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="23" t="s">
+      <c r="D58" s="21" t="s">
         <v>39</v>
       </c>
       <c r="E58" s="2" t="s">
@@ -5778,26 +5765,26 @@
         <f t="shared" si="6"/>
         <v>602.58000000000004</v>
       </c>
-      <c r="R58" s="20">
+      <c r="R58" s="19">
         <f t="shared" si="7"/>
         <v>43912</v>
       </c>
-      <c r="S58" s="20">
+      <c r="S58" s="19">
         <f t="shared" si="8"/>
         <v>43927</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>24830</v>
       </c>
       <c r="B59" s="2">
         <v>1</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D59" s="23" t="s">
+      <c r="D59" s="21" t="s">
         <v>33</v>
       </c>
       <c r="E59" s="2" t="s">
@@ -5846,26 +5833,26 @@
         <f t="shared" si="6"/>
         <v>132.66</v>
       </c>
-      <c r="R59" s="20">
+      <c r="R59" s="19">
         <f t="shared" si="7"/>
         <v>43927</v>
       </c>
-      <c r="S59" s="20">
+      <c r="S59" s="19">
         <f t="shared" si="8"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>24831</v>
       </c>
       <c r="B60" s="2">
         <v>1</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="21" t="s">
         <v>52</v>
       </c>
       <c r="E60" s="2" t="s">
@@ -5914,26 +5901,26 @@
         <f t="shared" si="6"/>
         <v>56.43</v>
       </c>
-      <c r="R60" s="20">
+      <c r="R60" s="19">
         <f t="shared" si="7"/>
         <v>43896</v>
       </c>
-      <c r="S60" s="20">
+      <c r="S60" s="19">
         <f t="shared" si="8"/>
         <v>43925</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>24833</v>
       </c>
       <c r="B61" s="2">
         <v>1</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="21" t="s">
         <v>58</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -5982,26 +5969,26 @@
         <f t="shared" si="6"/>
         <v>511.83</v>
       </c>
-      <c r="R61" s="20">
+      <c r="R61" s="19">
         <f t="shared" si="7"/>
         <v>43881</v>
       </c>
-      <c r="S61" s="20">
+      <c r="S61" s="19">
         <f t="shared" si="8"/>
         <v>43926</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>24837</v>
       </c>
       <c r="B62" s="2">
         <v>1</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="21" t="s">
         <v>72</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -6050,26 +6037,26 @@
         <f t="shared" si="6"/>
         <v>361.02</v>
       </c>
-      <c r="R62" s="20">
+      <c r="R62" s="19">
         <f t="shared" si="7"/>
         <v>43916</v>
       </c>
-      <c r="S62" s="20">
+      <c r="S62" s="19">
         <f t="shared" si="8"/>
         <v>43929</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>24838</v>
       </c>
       <c r="B63" s="2">
         <v>1</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="21" t="s">
         <v>51</v>
       </c>
       <c r="E63" s="2" t="s">
@@ -6118,26 +6105,26 @@
         <f t="shared" si="6"/>
         <v>668.25</v>
       </c>
-      <c r="R63" s="20">
+      <c r="R63" s="19">
         <f t="shared" si="7"/>
         <v>43932</v>
       </c>
-      <c r="S63" s="20">
+      <c r="S63" s="19">
         <f t="shared" si="8"/>
         <v>43948</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>24842</v>
       </c>
       <c r="B64" s="2">
         <v>1</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D64" s="23" t="s">
+      <c r="D64" s="21" t="s">
         <v>61</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -6186,26 +6173,26 @@
         <f t="shared" si="6"/>
         <v>126.72</v>
       </c>
-      <c r="R64" s="20">
+      <c r="R64" s="19">
         <f t="shared" si="7"/>
         <v>43914</v>
       </c>
-      <c r="S64" s="20">
+      <c r="S64" s="19">
         <f t="shared" si="8"/>
         <v>43933</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>24847</v>
       </c>
       <c r="B65" s="2">
         <v>1</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D65" s="23" t="s">
+      <c r="D65" s="21" t="s">
         <v>38</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -6254,26 +6241,26 @@
         <f t="shared" si="6"/>
         <v>1000.23</v>
       </c>
-      <c r="R65" s="20">
+      <c r="R65" s="19">
         <f t="shared" si="7"/>
         <v>43905</v>
       </c>
-      <c r="S65" s="20">
+      <c r="S65" s="19">
         <f t="shared" si="8"/>
         <v>43943</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>24851</v>
       </c>
       <c r="B66" s="2">
         <v>1</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D66" s="23" t="s">
+      <c r="D66" s="21" t="s">
         <v>63</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -6322,26 +6309,26 @@
         <f t="shared" si="6"/>
         <v>948.75</v>
       </c>
-      <c r="R66" s="20">
+      <c r="R66" s="19">
         <f t="shared" si="7"/>
         <v>43918</v>
       </c>
-      <c r="S66" s="20">
+      <c r="S66" s="19">
         <f t="shared" si="8"/>
         <v>43939</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>24854</v>
       </c>
       <c r="B67" s="2">
         <v>1</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D67" s="23" t="s">
+      <c r="D67" s="21" t="s">
         <v>57</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -6390,26 +6377,26 @@
         <f t="shared" ref="Q67:Q85" si="15">VALUE(SUBSTITUTE(SUBSTITUTE(F67,"S","$"),CHAR(160),""))</f>
         <v>446.49</v>
       </c>
-      <c r="R67" s="20">
+      <c r="R67" s="19">
         <f t="shared" ref="R67:R85" si="16">DATE(2020,MONTH(1&amp;M67),RIGHT(D67,2))</f>
         <v>43904</v>
       </c>
-      <c r="S67" s="20">
+      <c r="S67" s="19">
         <f t="shared" ref="S67:S85" si="17">DATE(2020,4,RIGHT(C67,2))</f>
         <v>43937</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>24857</v>
       </c>
       <c r="B68" s="2">
         <v>1</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D68" s="23" t="s">
+      <c r="D68" s="21" t="s">
         <v>45</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -6458,26 +6445,26 @@
         <f t="shared" si="15"/>
         <v>242.22</v>
       </c>
-      <c r="R68" s="20">
+      <c r="R68" s="19">
         <f t="shared" si="16"/>
         <v>43933</v>
       </c>
-      <c r="S68" s="20">
+      <c r="S68" s="19">
         <f t="shared" si="17"/>
         <v>43940</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>24861</v>
       </c>
       <c r="B69" s="2">
         <v>1</v>
       </c>
-      <c r="C69" s="23" t="s">
+      <c r="C69" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="21" t="s">
         <v>214</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -6526,26 +6513,26 @@
         <f t="shared" si="15"/>
         <v>600.6</v>
       </c>
-      <c r="R69" s="20">
+      <c r="R69" s="19">
         <f t="shared" si="16"/>
         <v>43887</v>
       </c>
-      <c r="S69" s="20">
+      <c r="S69" s="19">
         <f t="shared" si="17"/>
         <v>43929</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>24863</v>
       </c>
       <c r="B70" s="2">
         <v>1</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D70" s="23" t="s">
+      <c r="D70" s="21" t="s">
         <v>38</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -6594,26 +6581,26 @@
         <f t="shared" si="15"/>
         <v>546.80999999999995</v>
       </c>
-      <c r="R70" s="20">
+      <c r="R70" s="19">
         <f t="shared" si="16"/>
         <v>43905</v>
       </c>
-      <c r="S70" s="20">
+      <c r="S70" s="19">
         <f t="shared" si="17"/>
         <v>43942</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>24866</v>
       </c>
       <c r="B71" s="2">
         <v>1</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D71" s="23" t="s">
+      <c r="D71" s="21" t="s">
         <v>41</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -6662,26 +6649,26 @@
         <f t="shared" si="15"/>
         <v>840.51</v>
       </c>
-      <c r="R71" s="20">
+      <c r="R71" s="19">
         <f t="shared" si="16"/>
         <v>43900</v>
       </c>
-      <c r="S71" s="20">
+      <c r="S71" s="19">
         <f t="shared" si="17"/>
         <v>43931</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>24870</v>
       </c>
       <c r="B72" s="2">
         <v>1</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D72" s="23" t="s">
+      <c r="D72" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -6730,26 +6717,26 @@
         <f t="shared" si="15"/>
         <v>603.57000000000005</v>
       </c>
-      <c r="R72" s="20">
+      <c r="R72" s="19">
         <f t="shared" si="16"/>
         <v>43923</v>
       </c>
-      <c r="S72" s="20">
+      <c r="S72" s="19">
         <f t="shared" si="17"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>24873</v>
       </c>
       <c r="B73" s="2">
         <v>1</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="21" t="s">
         <v>61</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -6798,26 +6785,26 @@
         <f t="shared" si="15"/>
         <v>816.75</v>
       </c>
-      <c r="R73" s="20">
+      <c r="R73" s="19">
         <f t="shared" si="16"/>
         <v>43914</v>
       </c>
-      <c r="S73" s="20">
+      <c r="S73" s="19">
         <f t="shared" si="17"/>
         <v>43944</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>24875</v>
       </c>
       <c r="B74" s="2">
         <v>1</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D74" s="23" t="s">
+      <c r="D74" s="21" t="s">
         <v>39</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -6866,26 +6853,26 @@
         <f t="shared" si="15"/>
         <v>1065.57</v>
       </c>
-      <c r="R74" s="20">
+      <c r="R74" s="19">
         <f t="shared" si="16"/>
         <v>43912</v>
       </c>
-      <c r="S74" s="20">
+      <c r="S74" s="19">
         <f t="shared" si="17"/>
         <v>43951</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>24876</v>
       </c>
       <c r="B75" s="2">
         <v>1</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D75" s="23" t="s">
+      <c r="D75" s="21" t="s">
         <v>47</v>
       </c>
       <c r="E75" s="2" t="s">
@@ -6934,26 +6921,26 @@
         <f t="shared" si="15"/>
         <v>523.38</v>
       </c>
-      <c r="R75" s="20">
+      <c r="R75" s="19">
         <f t="shared" si="16"/>
         <v>43919</v>
       </c>
-      <c r="S75" s="20">
+      <c r="S75" s="19">
         <f t="shared" si="17"/>
         <v>43925</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>24877</v>
       </c>
       <c r="B76" s="2">
         <v>1</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="21" t="s">
         <v>108</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -7002,26 +6989,26 @@
         <f t="shared" si="15"/>
         <v>650.42999999999995</v>
       </c>
-      <c r="R76" s="20">
+      <c r="R76" s="19">
         <f t="shared" si="16"/>
         <v>43890</v>
       </c>
-      <c r="S76" s="20">
+      <c r="S76" s="19">
         <f t="shared" si="17"/>
         <v>43932</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>24878</v>
       </c>
       <c r="B77" s="2">
         <v>1</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="21" t="s">
         <v>24</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -7070,26 +7057,26 @@
         <f t="shared" si="15"/>
         <v>809.49</v>
       </c>
-      <c r="R77" s="20">
+      <c r="R77" s="19">
         <f t="shared" si="16"/>
         <v>43934</v>
       </c>
-      <c r="S77" s="20">
+      <c r="S77" s="19">
         <f t="shared" si="17"/>
         <v>43943</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>24880</v>
       </c>
       <c r="B78" s="2">
         <v>1</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D78" s="23" t="s">
+      <c r="D78" s="21" t="s">
         <v>27</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -7138,26 +7125,26 @@
         <f t="shared" si="15"/>
         <v>424.38</v>
       </c>
-      <c r="R78" s="20">
+      <c r="R78" s="19">
         <f t="shared" si="16"/>
         <v>43901</v>
       </c>
-      <c r="S78" s="20">
+      <c r="S78" s="19">
         <f t="shared" si="17"/>
         <v>43943</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>24882</v>
       </c>
       <c r="B79" s="2">
         <v>1</v>
       </c>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D79" s="23" t="s">
+      <c r="D79" s="21" t="s">
         <v>45</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -7206,26 +7193,26 @@
         <f t="shared" si="15"/>
         <v>955.68</v>
       </c>
-      <c r="R79" s="20">
+      <c r="R79" s="19">
         <f t="shared" si="16"/>
         <v>43933</v>
       </c>
-      <c r="S79" s="20">
+      <c r="S79" s="19">
         <f t="shared" si="17"/>
         <v>43935</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>24885</v>
       </c>
       <c r="B80" s="2">
         <v>1</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D80" s="23" t="s">
+      <c r="D80" s="21" t="s">
         <v>50</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -7274,26 +7261,26 @@
         <f t="shared" si="15"/>
         <v>764.28</v>
       </c>
-      <c r="R80" s="20">
+      <c r="R80" s="19">
         <f t="shared" si="16"/>
         <v>43942</v>
       </c>
-      <c r="S80" s="20">
+      <c r="S80" s="19">
         <f t="shared" si="17"/>
         <v>43950</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>24887</v>
       </c>
       <c r="B81" s="2">
         <v>1</v>
       </c>
-      <c r="C81" s="23" t="s">
+      <c r="C81" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="23" t="s">
+      <c r="D81" s="21" t="s">
         <v>29</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -7342,26 +7329,26 @@
         <f t="shared" si="15"/>
         <v>335.61</v>
       </c>
-      <c r="R81" s="20">
+      <c r="R81" s="19">
         <f t="shared" si="16"/>
         <v>43897</v>
       </c>
-      <c r="S81" s="20">
+      <c r="S81" s="19">
         <f t="shared" si="17"/>
         <v>43926</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>24891</v>
       </c>
       <c r="B82" s="2">
         <v>1</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D82" s="23" t="s">
+      <c r="D82" s="21" t="s">
         <v>23</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -7410,26 +7397,26 @@
         <f t="shared" si="15"/>
         <v>763.29</v>
       </c>
-      <c r="R82" s="20">
+      <c r="R82" s="19">
         <f t="shared" si="16"/>
         <v>43898</v>
       </c>
-      <c r="S82" s="20">
+      <c r="S82" s="19">
         <f t="shared" si="17"/>
         <v>43940</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>24893</v>
       </c>
       <c r="B83" s="2">
         <v>1</v>
       </c>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D83" s="23" t="s">
+      <c r="D83" s="21" t="s">
         <v>47</v>
       </c>
       <c r="E83" s="2" t="s">
@@ -7478,26 +7465,26 @@
         <f t="shared" si="15"/>
         <v>446.16</v>
       </c>
-      <c r="R83" s="20">
+      <c r="R83" s="19">
         <f t="shared" si="16"/>
         <v>43919</v>
       </c>
-      <c r="S83" s="20">
+      <c r="S83" s="19">
         <f t="shared" si="17"/>
         <v>43933</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>24898</v>
       </c>
       <c r="B84" s="2">
         <v>1</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D84" s="23" t="s">
+      <c r="D84" s="21" t="s">
         <v>23</v>
       </c>
       <c r="E84" s="2" t="s">
@@ -7546,26 +7533,26 @@
         <f t="shared" si="15"/>
         <v>1032.24</v>
       </c>
-      <c r="R84" s="20">
+      <c r="R84" s="19">
         <f t="shared" si="16"/>
         <v>43898</v>
       </c>
-      <c r="S84" s="20">
+      <c r="S84" s="19">
         <f t="shared" si="17"/>
         <v>43941</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>24902</v>
       </c>
       <c r="B85" s="2">
         <v>1</v>
       </c>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D85" s="23" t="s">
+      <c r="D85" s="21" t="s">
         <v>67</v>
       </c>
       <c r="E85" s="2" t="s">
@@ -7614,11 +7601,11 @@
         <f t="shared" si="15"/>
         <v>533.28</v>
       </c>
-      <c r="R85" s="20">
+      <c r="R85" s="19">
         <f t="shared" si="16"/>
         <v>43915</v>
       </c>
-      <c r="S85" s="20">
+      <c r="S85" s="19">
         <f t="shared" si="17"/>
         <v>43933</v>
       </c>
@@ -7633,4211 +7620,4209 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D059D34A-D0CE-45EB-8220-FA6C9F3EE824}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:N88"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="5" customWidth="1"/>
     <col min="6" max="6" width="14" style="5" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="8" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="8" customWidth="1"/>
-    <col min="14" max="14" width="12" style="8" customWidth="1"/>
+    <col min="9" max="10" width="13.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:14" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="N1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="20">
         <f ca="1">TODAY()</f>
-        <v>43872</v>
-      </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="21"/>
-      <c r="J2" s="9" t="s">
+        <v>46305</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2" s="20"/>
+      <c r="J2" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="M2" s="9" t="s">
+      <c r="K2" s="13"/>
+      <c r="M2" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="9">
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K3" s="5"/>
       <c r="M3" s="5"/>
-      <c r="N3"/>
-    </row>
-    <row r="4" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+    </row>
+    <row r="4" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="17" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="26">
         <f>545671</f>
         <v>545671</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="27">
         <v>43892</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="27">
         <f>WORKDAY(EDATE(D5,1)-1,1)</f>
         <v>43923</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="27">
         <v>43938</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="26">
         <v>223809</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="28">
         <v>742.5</v>
       </c>
-      <c r="K5" s="32" t="str">
+      <c r="K5" s="27" t="str">
         <f>TEXT(D5,"MMM")</f>
         <v>Mar</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="26">
         <f>DAY(D5)</f>
         <v>2</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="26">
         <f>IF(F5&gt;E5,NETWORKDAYS(E5,F5,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>10</v>
       </c>
-      <c r="N5" s="33">
-        <f>J5*M5*Penalty_Rate</f>
-        <v>26.73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="N5" s="28">
+        <f>M5*(J5*Penalty_Rate+flat_rate)</f>
+        <v>46.730000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="26">
         <v>545672</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="27">
         <v>43923</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="27">
         <f t="shared" ref="E6:E69" si="0">WORKDAY(EDATE(D6,1)-1,1)</f>
         <v>43955</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="27">
         <v>43941</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="26">
         <v>327600</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="29">
         <v>1021.02</v>
       </c>
-      <c r="K6" s="32" t="str">
+      <c r="K6" s="27" t="str">
         <f t="shared" ref="K6:K69" si="1">TEXT(D6,"MMM")</f>
         <v>Apr</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="26">
         <f t="shared" ref="L6:L69" si="2">DAY(D6)</f>
         <v>2</v>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="26">
         <f>IF(F6&gt;E6,NETWORKDAYS(E6,F6,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="33">
-        <f>J6*M6*Penalty_Rate</f>
+      <c r="N6" s="28">
+        <f>M6*(J6*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="26">
         <v>545674</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="27">
         <v>43906</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="27">
         <f t="shared" si="0"/>
         <v>43937</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="27">
         <v>43926</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="26">
         <v>332589</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="29">
         <v>409.53</v>
       </c>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="26">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="26">
         <f>IF(F7&gt;E7,NETWORKDAYS(E7,F7,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="33">
-        <f>J7*M7*Penalty_Rate</f>
+      <c r="N7" s="28">
+        <f>M7*(J7*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="26">
         <v>545676</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="27">
         <v>43915</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="27">
         <f t="shared" si="0"/>
         <v>43948</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="27">
         <v>43941</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="26">
         <v>337131</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="29">
         <v>-234.96</v>
       </c>
-      <c r="K8" s="32" t="str">
+      <c r="K8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="26">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="M8" s="34">
+      <c r="M8" s="26">
         <f>IF(F8&gt;E8,NETWORKDAYS(E8,F8,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="33">
-        <f>J8*M8*Penalty_Rate</f>
+      <c r="N8" s="28">
+        <f>M8*(J8*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="26">
         <v>545677</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="27">
         <v>43907</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="27">
         <f t="shared" si="0"/>
         <v>43938</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="27">
         <v>43931</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="26">
         <v>319376</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="29">
         <v>-450.12</v>
       </c>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="26">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="26">
         <f>IF(F9&gt;E9,NETWORKDAYS(E9,F9,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="33">
-        <f>J9*M9*Penalty_Rate</f>
+      <c r="N9" s="28">
+        <f>M9*(J9*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="26">
         <v>545678</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="27">
         <v>43930</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="27">
         <f t="shared" si="0"/>
         <v>43962</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="27">
         <v>43951</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="26">
         <v>334724</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="29">
         <v>114.18</v>
       </c>
-      <c r="K10" s="32" t="str">
+      <c r="K10" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="26">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="26">
         <f>IF(F10&gt;E10,NETWORKDAYS(E10,F10,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="33">
-        <f>J10*M10*Penalty_Rate</f>
+      <c r="N10" s="28">
+        <f>M10*(J10*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="26">
         <v>545679</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="27">
         <v>43913</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="27">
         <f t="shared" si="0"/>
         <v>43944</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="27">
         <v>43951</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="26">
         <v>310607</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="29">
         <v>930.93</v>
       </c>
-      <c r="K11" s="32" t="str">
+      <c r="K11" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="26">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="26">
         <f>IF(F11&gt;E11,NETWORKDAYS(E11,F11,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>6</v>
       </c>
-      <c r="N11" s="33">
-        <f>J11*M11*Penalty_Rate</f>
-        <v>20.108087999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="N11" s="28">
+        <f>M11*(J11*Penalty_Rate+flat_rate)</f>
+        <v>32.108087999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="26">
         <v>545681</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="27">
         <v>43917</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="27">
         <f t="shared" si="0"/>
         <v>43948</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="27">
         <v>43935</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="26">
         <v>226225</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="29">
         <v>466.29</v>
       </c>
-      <c r="K12" s="32" t="str">
+      <c r="K12" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="26">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="26">
         <f>IF(F12&gt;E12,NETWORKDAYS(E12,F12,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="33">
-        <f>J12*M12*Penalty_Rate</f>
+      <c r="N12" s="28">
+        <f>M12*(J12*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="26">
         <v>545682</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="27">
         <v>43912</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="27">
         <f t="shared" si="0"/>
         <v>43943</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="27">
         <v>43948</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="26">
         <v>223858</v>
       </c>
-      <c r="I13" s="31" t="s">
+      <c r="I13" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="29">
         <v>222.42</v>
       </c>
-      <c r="K13" s="32" t="str">
+      <c r="K13" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="26">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="26">
         <f>IF(F13&gt;E13,NETWORKDAYS(E13,F13,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>4</v>
       </c>
-      <c r="N13" s="33">
-        <f>J13*M13*Penalty_Rate</f>
-        <v>3.2028479999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="N13" s="28">
+        <f>M13*(J13*Penalty_Rate+flat_rate)</f>
+        <v>11.202847999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="26">
         <v>545683</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="27">
         <v>43899</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="27">
         <f t="shared" si="0"/>
         <v>43930</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="27">
         <v>43932</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="26">
         <v>211781</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="29">
         <v>679.8</v>
       </c>
-      <c r="K14" s="32" t="str">
+      <c r="K14" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="26">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="26">
         <f>IF(F14&gt;E14,NETWORKDAYS(E14,F14,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>1</v>
       </c>
-      <c r="N14" s="33">
-        <f>J14*M14*Penalty_Rate</f>
-        <v>2.4472799999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="N14" s="28">
+        <f>M14*(J14*Penalty_Rate+flat_rate)</f>
+        <v>4.4472799999999992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="26">
         <v>545685</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="27">
         <v>43925</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="27">
         <f t="shared" si="0"/>
         <v>43955</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="27">
         <v>43944</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="26">
         <v>232805</v>
       </c>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="29">
         <v>171.93</v>
       </c>
-      <c r="K15" s="32" t="str">
+      <c r="K15" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="26">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="26">
         <f>IF(F15&gt;E15,NETWORKDAYS(E15,F15,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="33">
-        <f>J15*M15*Penalty_Rate</f>
+      <c r="N15" s="28">
+        <f>M15*(J15*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="26">
         <v>545687</v>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="27">
         <v>43885</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="27">
         <f t="shared" si="0"/>
         <v>43914</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="27">
         <v>43927</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="26">
         <v>312187</v>
       </c>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="29">
         <v>623.70000000000005</v>
       </c>
-      <c r="K16" s="32" t="str">
+      <c r="K16" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="26">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="26">
         <f>IF(F16&gt;E16,NETWORKDAYS(E16,F16,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>10</v>
       </c>
-      <c r="N16" s="33">
-        <f>J16*M16*Penalty_Rate</f>
-        <v>22.453199999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="N16" s="28">
+        <f>M16*(J16*Penalty_Rate+flat_rate)</f>
+        <v>42.453199999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="26">
         <v>545689</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="27">
         <v>43919</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="27">
         <f t="shared" si="0"/>
         <v>43950</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="27">
         <v>43945</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="26">
         <v>319790</v>
       </c>
-      <c r="I17" s="31" t="s">
+      <c r="I17" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="29">
         <v>221.1</v>
       </c>
-      <c r="K17" s="32" t="str">
+      <c r="K17" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="26">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="26">
         <f>IF(F17&gt;E17,NETWORKDAYS(E17,F17,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="33">
-        <f>J17*M17*Penalty_Rate</f>
+      <c r="N17" s="28">
+        <f>M17*(J17*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="26">
         <v>545690</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="27">
         <v>43930</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="27">
         <f t="shared" si="0"/>
         <v>43962</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="27">
         <v>43949</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="26">
         <v>327342</v>
       </c>
-      <c r="I18" s="31" t="s">
+      <c r="I18" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="29">
         <v>393.36</v>
       </c>
-      <c r="K18" s="32" t="str">
+      <c r="K18" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="26">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="26">
         <f>IF(F18&gt;E18,NETWORKDAYS(E18,F18,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="33">
-        <f>J18*M18*Penalty_Rate</f>
+      <c r="N18" s="28">
+        <f>M18*(J18*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="26">
         <v>545691</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="27">
         <v>43899</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="27">
         <f t="shared" si="0"/>
         <v>43930</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="27">
         <v>43942</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="26">
         <v>335460</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="29">
         <v>642.17999999999995</v>
       </c>
-      <c r="K19" s="32" t="str">
+      <c r="K19" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="26">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="26">
         <f>IF(F19&gt;E19,NETWORKDAYS(E19,F19,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>7</v>
       </c>
-      <c r="N19" s="33">
-        <f>J19*M19*Penalty_Rate</f>
-        <v>16.182935999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="N19" s="28">
+        <f>M19*(J19*Penalty_Rate+flat_rate)</f>
+        <v>30.182935999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="26">
         <v>545692</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="27">
         <v>43909</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="27">
         <f t="shared" si="0"/>
         <v>43941</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="27">
         <v>43951</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="26">
         <v>323955</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="29">
         <v>499.95</v>
       </c>
-      <c r="K20" s="32" t="str">
+      <c r="K20" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="26">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="26">
         <f>IF(F20&gt;E20,NETWORKDAYS(E20,F20,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>9</v>
       </c>
-      <c r="N20" s="33">
-        <f>J20*M20*Penalty_Rate</f>
-        <v>16.19838</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="N20" s="28">
+        <f>M20*(J20*Penalty_Rate+flat_rate)</f>
+        <v>34.19838</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="26">
         <v>545693</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="27">
         <v>43890</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="27">
         <f t="shared" si="0"/>
         <v>43920</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="27">
         <v>43928</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="26">
         <v>316515</v>
       </c>
-      <c r="I21" s="31" t="s">
+      <c r="I21" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="29">
         <v>299.64</v>
       </c>
-      <c r="K21" s="32" t="str">
+      <c r="K21" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="26">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="26">
         <f>IF(F21&gt;E21,NETWORKDAYS(E21,F21,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>7</v>
       </c>
-      <c r="N21" s="33">
-        <f>J21*M21*Penalty_Rate</f>
-        <v>7.5509279999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
+      <c r="N21" s="28">
+        <f>M21*(J21*Penalty_Rate+flat_rate)</f>
+        <v>21.550927999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="26">
         <v>545695</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="27">
         <v>43912</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="27">
         <f t="shared" si="0"/>
         <v>43943</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="27">
         <v>43951</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="26">
         <v>231320</v>
       </c>
-      <c r="I22" s="31" t="s">
+      <c r="I22" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="29">
         <v>312.83999999999997</v>
       </c>
-      <c r="K22" s="32" t="str">
+      <c r="K22" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L22" s="26">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="M22" s="34">
+      <c r="M22" s="26">
         <f>IF(F22&gt;E22,NETWORKDAYS(E22,F22,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>7</v>
       </c>
-      <c r="N22" s="33">
-        <f>J22*M22*Penalty_Rate</f>
-        <v>7.8835679999999986</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="N22" s="28">
+        <f>M22*(J22*Penalty_Rate+flat_rate)</f>
+        <v>21.883567999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="26">
         <v>545696</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="27">
         <v>43904</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="27">
         <f t="shared" si="0"/>
         <v>43935</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="27">
         <v>43926</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H23" s="31">
+      <c r="H23" s="26">
         <v>213670</v>
       </c>
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="29">
         <v>993.63</v>
       </c>
-      <c r="K23" s="32" t="str">
+      <c r="K23" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="26">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="26">
         <f>IF(F23&gt;E23,NETWORKDAYS(E23,F23,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="33">
-        <f>J23*M23*Penalty_Rate</f>
+      <c r="N23" s="28">
+        <f>M23*(J23*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="26">
         <v>545697</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="27">
         <v>43917</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="27">
         <f t="shared" si="0"/>
         <v>43948</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="27">
         <v>43922</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="26">
         <v>226166</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="29">
         <v>1053.69</v>
       </c>
-      <c r="K24" s="32" t="str">
+      <c r="K24" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="26">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="26">
         <f>IF(F24&gt;E24,NETWORKDAYS(E24,F24,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="33">
-        <f>J24*M24*Penalty_Rate</f>
+      <c r="N24" s="28">
+        <f>M24*(J24*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="26">
         <v>545698</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="27">
         <v>43929</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="27">
         <f t="shared" si="0"/>
         <v>43959</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="27">
         <v>43951</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="26">
         <v>316479</v>
       </c>
-      <c r="I25" s="31" t="s">
+      <c r="I25" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="29">
         <v>1047.75</v>
       </c>
-      <c r="K25" s="32" t="str">
+      <c r="K25" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="26">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="26">
         <f>IF(F25&gt;E25,NETWORKDAYS(E25,F25,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N25" s="33">
-        <f>J25*M25*Penalty_Rate</f>
+      <c r="N25" s="28">
+        <f>M25*(J25*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="26">
         <v>545700</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="27">
         <v>43888</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="27">
         <f t="shared" si="0"/>
         <v>43917</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="27">
         <v>43929</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="26">
         <v>230046</v>
       </c>
-      <c r="I26" s="31" t="s">
+      <c r="I26" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="29">
         <v>1096.92</v>
       </c>
-      <c r="K26" s="32" t="str">
+      <c r="K26" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="26">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="26">
         <f>IF(F26&gt;E26,NETWORKDAYS(E26,F26,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>9</v>
       </c>
-      <c r="N26" s="33">
-        <f>J26*M26*Penalty_Rate</f>
-        <v>35.540208</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="N26" s="28">
+        <f>M26*(J26*Penalty_Rate+flat_rate)</f>
+        <v>53.540208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="26">
         <v>545702</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="27">
         <v>43886</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="27">
         <f t="shared" si="0"/>
         <v>43915</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="27">
         <v>43928</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="26">
         <v>224680</v>
       </c>
-      <c r="I27" s="31" t="s">
+      <c r="I27" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="29">
         <v>257.07</v>
       </c>
-      <c r="K27" s="32" t="str">
+      <c r="K27" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="26">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="26">
         <f>IF(F27&gt;E27,NETWORKDAYS(E27,F27,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>10</v>
       </c>
-      <c r="N27" s="33">
-        <f>J27*M27*Penalty_Rate</f>
-        <v>9.2545199999999994</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="N27" s="28">
+        <f>M27*(J27*Penalty_Rate+flat_rate)</f>
+        <v>29.254519999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="26">
         <v>545703</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="27">
         <v>43945</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="27">
         <f t="shared" si="0"/>
         <v>43976</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="27">
         <v>43949</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="26">
         <v>238023</v>
       </c>
-      <c r="I28" s="31" t="s">
+      <c r="I28" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="29">
         <v>215.49</v>
       </c>
-      <c r="K28" s="32" t="str">
+      <c r="K28" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="26">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="26">
         <f>IF(F28&gt;E28,NETWORKDAYS(E28,F28,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="33">
-        <f>J28*M28*Penalty_Rate</f>
+      <c r="N28" s="28">
+        <f>M28*(J28*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="26">
         <v>545705</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="27">
         <v>43926</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="27">
         <f t="shared" si="0"/>
         <v>43956</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="27">
         <v>43945</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H29" s="31">
+      <c r="H29" s="26">
         <v>224184</v>
       </c>
-      <c r="I29" s="31" t="s">
+      <c r="I29" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="29">
         <v>455.07</v>
       </c>
-      <c r="K29" s="32" t="str">
+      <c r="K29" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="26">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M29" s="34">
+      <c r="M29" s="26">
         <f>IF(F29&gt;E29,NETWORKDAYS(E29,F29,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N29" s="33">
-        <f>J29*M29*Penalty_Rate</f>
+      <c r="N29" s="28">
+        <f>M29*(J29*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="26">
         <v>545706</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="27">
         <v>43923</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="27">
         <f t="shared" si="0"/>
         <v>43955</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="27">
         <v>43930</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H30" s="31">
+      <c r="H30" s="26">
         <v>216205</v>
       </c>
-      <c r="I30" s="31" t="s">
+      <c r="I30" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="29">
         <v>711.81</v>
       </c>
-      <c r="K30" s="32" t="str">
+      <c r="K30" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="26">
         <f>IF(F30&gt;E30,NETWORKDAYS(E30,F30,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="33">
-        <f>J30*M30*Penalty_Rate</f>
+      <c r="N30" s="28">
+        <f>M30*(J30*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="26">
         <v>545707</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="27">
         <v>43911</v>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="27">
         <f t="shared" si="0"/>
         <v>43942</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="27">
         <v>43925</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H31" s="31">
+      <c r="H31" s="26">
         <v>331383</v>
       </c>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="29">
         <v>78.540000000000006</v>
       </c>
-      <c r="K31" s="32" t="str">
+      <c r="K31" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="26">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="26">
         <f>IF(F31&gt;E31,NETWORKDAYS(E31,F31,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="33">
-        <f>J31*M31*Penalty_Rate</f>
+      <c r="N31" s="28">
+        <f>M31*(J31*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="26">
         <v>545708</v>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="27">
         <v>43892</v>
       </c>
-      <c r="E32" s="32">
+      <c r="E32" s="27">
         <f t="shared" si="0"/>
         <v>43923</v>
       </c>
-      <c r="F32" s="32">
+      <c r="F32" s="27">
         <v>43927</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="G32" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H32" s="31">
+      <c r="H32" s="26">
         <v>335282</v>
       </c>
-      <c r="I32" s="31" t="s">
+      <c r="I32" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="29">
         <v>302.61</v>
       </c>
-      <c r="K32" s="32" t="str">
+      <c r="K32" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L32" s="34">
+      <c r="L32" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M32" s="34">
+      <c r="M32" s="26">
         <f>IF(F32&gt;E32,NETWORKDAYS(E32,F32,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>3</v>
       </c>
-      <c r="N32" s="33">
-        <f>J32*M32*Penalty_Rate</f>
-        <v>3.2681879999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="N32" s="28">
+        <f>M32*(J32*Penalty_Rate+flat_rate)</f>
+        <v>9.2681879999999985</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="26">
         <v>545710</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="27">
         <v>43886</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="27">
         <f t="shared" si="0"/>
         <v>43915</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="27">
         <v>43931</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="26">
         <v>330858</v>
       </c>
-      <c r="I33" s="31" t="s">
+      <c r="I33" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="29">
         <v>426.03</v>
       </c>
-      <c r="K33" s="32" t="str">
+      <c r="K33" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="26">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="26">
         <f>IF(F33&gt;E33,NETWORKDAYS(E33,F33,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>12</v>
       </c>
-      <c r="N33" s="33">
-        <f>J33*M33*Penalty_Rate</f>
-        <v>18.404495999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+      <c r="N33" s="28">
+        <f>M33*(J33*Penalty_Rate+flat_rate)</f>
+        <v>42.404495999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="26">
         <v>545711</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="27">
         <v>43899</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="27">
         <f t="shared" si="0"/>
         <v>43930</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="27">
         <v>43932</v>
       </c>
-      <c r="G34" s="31" t="s">
+      <c r="G34" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="26">
         <v>238202</v>
       </c>
-      <c r="I34" s="31" t="s">
+      <c r="I34" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="29">
         <v>489.72</v>
       </c>
-      <c r="K34" s="32" t="str">
+      <c r="K34" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="26">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="26">
         <f>IF(F34&gt;E34,NETWORKDAYS(E34,F34,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>1</v>
       </c>
-      <c r="N34" s="33">
-        <f>J34*M34*Penalty_Rate</f>
-        <v>1.7629920000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="N34" s="28">
+        <f>M34*(J34*Penalty_Rate+flat_rate)</f>
+        <v>3.7629920000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="26">
         <v>545713</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="27">
         <v>43915</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="27">
         <f t="shared" si="0"/>
         <v>43948</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="27">
         <v>43949</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="26">
         <v>217217</v>
       </c>
-      <c r="I35" s="31" t="s">
+      <c r="I35" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="29">
         <v>352.44</v>
       </c>
-      <c r="K35" s="32" t="str">
+      <c r="K35" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="26">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="26">
         <f>IF(F35&gt;E35,NETWORKDAYS(E35,F35,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>2</v>
       </c>
-      <c r="N35" s="33">
-        <f>J35*M35*Penalty_Rate</f>
-        <v>2.5375679999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+      <c r="N35" s="28">
+        <f>M35*(J35*Penalty_Rate+flat_rate)</f>
+        <v>6.5375680000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="26">
         <v>545715</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="27">
         <v>43912</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="27">
         <f t="shared" si="0"/>
         <v>43943</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="27">
         <v>43937</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H36" s="31">
+      <c r="H36" s="26">
         <v>234637</v>
       </c>
-      <c r="I36" s="31" t="s">
+      <c r="I36" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="29">
         <v>238.59</v>
       </c>
-      <c r="K36" s="32" t="str">
+      <c r="K36" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="26">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="26">
         <f>IF(F36&gt;E36,NETWORKDAYS(E36,F36,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="33">
-        <f>J36*M36*Penalty_Rate</f>
+      <c r="N36" s="28">
+        <f>M36*(J36*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="26">
         <v>545716</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D37" s="27">
         <v>43936</v>
       </c>
-      <c r="E37" s="32">
+      <c r="E37" s="27">
         <f t="shared" si="0"/>
         <v>43966</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="27">
         <v>43941</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H37" s="31">
+      <c r="H37" s="26">
         <v>332725</v>
       </c>
-      <c r="I37" s="31" t="s">
+      <c r="I37" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="29">
         <v>549.12</v>
       </c>
-      <c r="K37" s="32" t="str">
+      <c r="K37" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L37" s="34">
+      <c r="L37" s="26">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="M37" s="34">
+      <c r="M37" s="26">
         <f>IF(F37&gt;E37,NETWORKDAYS(E37,F37,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N37" s="33">
-        <f>J37*M37*Penalty_Rate</f>
+      <c r="N37" s="28">
+        <f>M37*(J37*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="26">
         <v>545718</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="27">
         <v>43893</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="27">
         <f t="shared" si="0"/>
         <v>43924</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="27">
         <v>43923</v>
       </c>
-      <c r="G38" s="31" t="s">
+      <c r="G38" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="26">
         <v>227351</v>
       </c>
-      <c r="I38" s="31" t="s">
+      <c r="I38" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="29">
         <v>322.41000000000003</v>
       </c>
-      <c r="K38" s="32" t="str">
+      <c r="K38" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="26">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="26">
         <f>IF(F38&gt;E38,NETWORKDAYS(E38,F38,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N38" s="33">
-        <f>J38*M38*Penalty_Rate</f>
+      <c r="N38" s="28">
+        <f>M38*(J38*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="26">
         <v>545719</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="27">
         <v>43892</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="27">
         <f t="shared" si="0"/>
         <v>43923</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="27">
         <v>43934</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="26">
         <v>336345</v>
       </c>
-      <c r="I39" s="31" t="s">
+      <c r="I39" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="29">
         <v>644.82000000000005</v>
       </c>
-      <c r="K39" s="32" t="str">
+      <c r="K39" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="26">
         <f>IF(F39&gt;E39,NETWORKDAYS(E39,F39,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>6</v>
       </c>
-      <c r="N39" s="33">
-        <f>J39*M39*Penalty_Rate</f>
-        <v>13.928112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
+      <c r="N39" s="28">
+        <f>M39*(J39*Penalty_Rate+flat_rate)</f>
+        <v>25.928111999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="26">
         <v>545721</v>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="27">
         <v>43923</v>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="27">
         <f t="shared" si="0"/>
         <v>43955</v>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="27">
         <v>43944</v>
       </c>
-      <c r="G40" s="31" t="s">
+      <c r="G40" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="26">
         <v>338595</v>
       </c>
-      <c r="I40" s="31" t="s">
+      <c r="I40" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J40" s="35">
+      <c r="J40" s="29">
         <v>113.19</v>
       </c>
-      <c r="K40" s="32" t="str">
+      <c r="K40" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L40" s="34">
+      <c r="L40" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M40" s="34">
+      <c r="M40" s="26">
         <f>IF(F40&gt;E40,NETWORKDAYS(E40,F40,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N40" s="33">
-        <f>J40*M40*Penalty_Rate</f>
+      <c r="N40" s="28">
+        <f>M40*(J40*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="26">
         <v>545722</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="27">
         <v>43941</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="27">
         <f t="shared" si="0"/>
         <v>43971</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="27">
         <v>43949</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="26">
         <v>325149</v>
       </c>
-      <c r="I41" s="31" t="s">
+      <c r="I41" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="29">
         <v>449.13</v>
       </c>
-      <c r="K41" s="32" t="str">
+      <c r="K41" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="26">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="26">
         <f>IF(F41&gt;E41,NETWORKDAYS(E41,F41,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N41" s="33">
-        <f>J41*M41*Penalty_Rate</f>
+      <c r="N41" s="28">
+        <f>M41*(J41*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="31" t="s">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="26">
         <v>545723</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="27">
         <v>43911</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="27">
         <f t="shared" si="0"/>
         <v>43942</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="27">
         <v>43933</v>
       </c>
-      <c r="G42" s="31" t="s">
+      <c r="G42" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="26">
         <v>227994</v>
       </c>
-      <c r="I42" s="31" t="s">
+      <c r="I42" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="29">
         <v>819.06</v>
       </c>
-      <c r="K42" s="32" t="str">
+      <c r="K42" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="26">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="26">
         <f>IF(F42&gt;E42,NETWORKDAYS(E42,F42,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N42" s="33">
-        <f>J42*M42*Penalty_Rate</f>
+      <c r="N42" s="28">
+        <f>M42*(J42*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="26">
         <v>545724</v>
       </c>
-      <c r="D43" s="32">
+      <c r="D43" s="27">
         <v>43880</v>
       </c>
-      <c r="E43" s="32">
+      <c r="E43" s="27">
         <f t="shared" si="0"/>
         <v>43909</v>
       </c>
-      <c r="F43" s="32">
+      <c r="F43" s="27">
         <v>43924</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H43" s="31">
+      <c r="H43" s="26">
         <v>222399</v>
       </c>
-      <c r="I43" s="31" t="s">
+      <c r="I43" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J43" s="35">
+      <c r="J43" s="29">
         <v>1019.04</v>
       </c>
-      <c r="K43" s="32" t="str">
+      <c r="K43" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L43" s="34">
+      <c r="L43" s="26">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="M43" s="34">
+      <c r="M43" s="26">
         <f>IF(F43&gt;E43,NETWORKDAYS(E43,F43,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>12</v>
       </c>
-      <c r="N43" s="33">
-        <f>J43*M43*Penalty_Rate</f>
-        <v>44.022527999999994</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+      <c r="N43" s="28">
+        <f>M43*(J43*Penalty_Rate+flat_rate)</f>
+        <v>68.022527999999994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="26">
         <v>545725</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="27">
         <v>43919</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="27">
         <f t="shared" si="0"/>
         <v>43950</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="27">
         <v>43935</v>
       </c>
-      <c r="G44" s="31" t="s">
+      <c r="G44" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="26">
         <v>316436</v>
       </c>
-      <c r="I44" s="31" t="s">
+      <c r="I44" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="29">
         <v>736.23</v>
       </c>
-      <c r="K44" s="32" t="str">
+      <c r="K44" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="26">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="26">
         <f>IF(F44&gt;E44,NETWORKDAYS(E44,F44,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N44" s="33">
-        <f>J44*M44*Penalty_Rate</f>
+      <c r="N44" s="28">
+        <f>M44*(J44*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="31" t="s">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="26">
         <v>545726</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="27">
         <v>43895</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="27">
         <f t="shared" si="0"/>
         <v>43927</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="27">
         <v>43937</v>
       </c>
-      <c r="G45" s="31" t="s">
+      <c r="G45" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="26">
         <v>312603</v>
       </c>
-      <c r="I45" s="31" t="s">
+      <c r="I45" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="29">
         <v>-600.27</v>
       </c>
-      <c r="K45" s="32" t="str">
+      <c r="K45" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="26">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M45" s="34">
+      <c r="M45" s="26">
         <f>IF(F45&gt;E45,NETWORKDAYS(E45,F45,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>7</v>
       </c>
-      <c r="N45" s="33">
-        <f>J45*M45*Penalty_Rate</f>
-        <v>-15.126803999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+      <c r="N45" s="28">
+        <f>M45*(J45*Penalty_Rate+flat_rate)</f>
+        <v>-1.1268039999999977</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="26">
         <v>545727</v>
       </c>
-      <c r="D46" s="32">
+      <c r="D46" s="27">
         <v>43907</v>
       </c>
-      <c r="E46" s="32">
+      <c r="E46" s="27">
         <f t="shared" si="0"/>
         <v>43938</v>
       </c>
-      <c r="F46" s="32">
+      <c r="F46" s="27">
         <v>43929</v>
       </c>
-      <c r="G46" s="31" t="s">
+      <c r="G46" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="26">
         <v>339907</v>
       </c>
-      <c r="I46" s="31" t="s">
+      <c r="I46" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J46" s="35">
+      <c r="J46" s="29">
         <v>480.81</v>
       </c>
-      <c r="K46" s="32" t="str">
+      <c r="K46" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L46" s="34">
+      <c r="L46" s="26">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="M46" s="34">
+      <c r="M46" s="26">
         <f>IF(F46&gt;E46,NETWORKDAYS(E46,F46,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N46" s="33">
-        <f>J46*M46*Penalty_Rate</f>
+      <c r="N46" s="28">
+        <f>M46*(J46*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="26">
         <v>545729</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="27">
         <v>43908</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="27">
         <f t="shared" si="0"/>
         <v>43941</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="27">
         <v>43948</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="26">
         <v>218463</v>
       </c>
-      <c r="I47" s="31" t="s">
+      <c r="I47" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="29">
         <v>253.77</v>
       </c>
-      <c r="K47" s="32" t="str">
+      <c r="K47" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L47" s="34">
+      <c r="L47" s="26">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="M47" s="34">
+      <c r="M47" s="26">
         <f>IF(F47&gt;E47,NETWORKDAYS(E47,F47,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>6</v>
       </c>
-      <c r="N47" s="33">
-        <f>J47*M47*Penalty_Rate</f>
-        <v>5.4814319999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="31" t="s">
+      <c r="N47" s="28">
+        <f>M47*(J47*Penalty_Rate+flat_rate)</f>
+        <v>17.481432000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="26">
         <v>545731</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="27">
         <v>43906</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="27">
         <f t="shared" si="0"/>
         <v>43937</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="27">
         <v>43949</v>
       </c>
-      <c r="G48" s="31" t="s">
+      <c r="G48" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="26">
         <v>336345</v>
       </c>
-      <c r="I48" s="31" t="s">
+      <c r="I48" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J48" s="35">
+      <c r="J48" s="29">
         <v>442.86</v>
       </c>
-      <c r="K48" s="32" t="str">
+      <c r="K48" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L48" s="34">
+      <c r="L48" s="26">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="M48" s="34">
+      <c r="M48" s="26">
         <f>IF(F48&gt;E48,NETWORKDAYS(E48,F48,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>9</v>
       </c>
-      <c r="N48" s="33">
-        <f>J48*M48*Penalty_Rate</f>
-        <v>14.348664000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="31" t="s">
+      <c r="N48" s="28">
+        <f>M48*(J48*Penalty_Rate+flat_rate)</f>
+        <v>32.348663999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="26">
         <v>545732</v>
       </c>
-      <c r="D49" s="32">
+      <c r="D49" s="27">
         <v>43901</v>
       </c>
-      <c r="E49" s="32">
+      <c r="E49" s="27">
         <f t="shared" si="0"/>
         <v>43934</v>
       </c>
-      <c r="F49" s="32">
+      <c r="F49" s="27">
         <v>43924</v>
       </c>
-      <c r="G49" s="31" t="s">
+      <c r="G49" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H49" s="31">
+      <c r="H49" s="26">
         <v>227664</v>
       </c>
-      <c r="I49" s="31" t="s">
+      <c r="I49" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="35">
+      <c r="J49" s="29">
         <v>630.96</v>
       </c>
-      <c r="K49" s="32" t="str">
+      <c r="K49" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L49" s="34">
+      <c r="L49" s="26">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="M49" s="34">
+      <c r="M49" s="26">
         <f>IF(F49&gt;E49,NETWORKDAYS(E49,F49,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N49" s="33">
-        <f>J49*M49*Penalty_Rate</f>
+      <c r="N49" s="28">
+        <f>M49*(J49*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="26">
         <v>545734</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="27">
         <v>43895</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="27">
         <f t="shared" si="0"/>
         <v>43927</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="27">
         <v>43925</v>
       </c>
-      <c r="G50" s="31" t="s">
+      <c r="G50" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="26">
         <v>331460</v>
       </c>
-      <c r="I50" s="31" t="s">
+      <c r="I50" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J50" s="35">
+      <c r="J50" s="29">
         <v>821.37</v>
       </c>
-      <c r="K50" s="32" t="str">
+      <c r="K50" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="26">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="26">
         <f>IF(F50&gt;E50,NETWORKDAYS(E50,F50,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N50" s="33">
-        <f>J50*M50*Penalty_Rate</f>
+      <c r="N50" s="28">
+        <f>M50*(J50*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="31" t="s">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="26">
         <v>545735</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="27">
         <v>43888</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="27">
         <f t="shared" si="0"/>
         <v>43917</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="27">
         <v>43928</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="26">
         <v>327740</v>
       </c>
-      <c r="I51" s="31" t="s">
+      <c r="I51" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J51" s="35">
+      <c r="J51" s="29">
         <v>950.73</v>
       </c>
-      <c r="K51" s="32" t="str">
+      <c r="K51" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="26">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="M51" s="34">
+      <c r="M51" s="26">
         <f>IF(F51&gt;E51,NETWORKDAYS(E51,F51,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>8</v>
       </c>
-      <c r="N51" s="33">
-        <f>J51*M51*Penalty_Rate</f>
-        <v>27.381024</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="31" t="s">
+      <c r="N51" s="28">
+        <f>M51*(J51*Penalty_Rate+flat_rate)</f>
+        <v>43.381023999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="26">
         <v>545737</v>
       </c>
-      <c r="D52" s="32">
+      <c r="D52" s="27">
         <v>43921</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="27">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
-      <c r="F52" s="32">
+      <c r="F52" s="27">
         <v>43931</v>
       </c>
-      <c r="G52" s="31" t="s">
+      <c r="G52" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H52" s="31">
+      <c r="H52" s="26">
         <v>221183</v>
       </c>
-      <c r="I52" s="31" t="s">
+      <c r="I52" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J52" s="35">
+      <c r="J52" s="29">
         <v>956.34</v>
       </c>
-      <c r="K52" s="32" t="str">
+      <c r="K52" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L52" s="34">
+      <c r="L52" s="26">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="M52" s="34">
+      <c r="M52" s="26">
         <f>IF(F52&gt;E52,NETWORKDAYS(E52,F52,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N52" s="33">
-        <f>J52*M52*Penalty_Rate</f>
+      <c r="N52" s="28">
+        <f>M52*(J52*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="31" t="s">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="26">
         <v>545739</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="27">
         <v>43917</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="27">
         <f t="shared" si="0"/>
         <v>43948</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="27">
         <v>43933</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="26">
         <v>214234</v>
       </c>
-      <c r="I53" s="31" t="s">
+      <c r="I53" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J53" s="35">
+      <c r="J53" s="29">
         <v>1094.28</v>
       </c>
-      <c r="K53" s="32" t="str">
+      <c r="K53" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="26">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="M53" s="34">
+      <c r="M53" s="26">
         <f>IF(F53&gt;E53,NETWORKDAYS(E53,F53,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N53" s="33">
-        <f>J53*M53*Penalty_Rate</f>
+      <c r="N53" s="28">
+        <f>M53*(J53*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="B54" s="31" t="s">
+      <c r="B54" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="26">
         <v>545740</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="27">
         <v>43908</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="27">
         <f t="shared" si="0"/>
         <v>43941</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="27">
         <v>43926</v>
       </c>
-      <c r="G54" s="31" t="s">
+      <c r="G54" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="26">
         <v>321456</v>
       </c>
-      <c r="I54" s="31" t="s">
+      <c r="I54" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J54" s="35">
+      <c r="J54" s="29">
         <v>628.98</v>
       </c>
-      <c r="K54" s="32" t="str">
+      <c r="K54" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L54" s="34">
+      <c r="L54" s="26">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="M54" s="34">
+      <c r="M54" s="26">
         <f>IF(F54&gt;E54,NETWORKDAYS(E54,F54,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N54" s="33">
-        <f>J54*M54*Penalty_Rate</f>
+      <c r="N54" s="28">
+        <f>M54*(J54*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="31" t="s">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="B55" s="31" t="s">
+      <c r="B55" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="26">
         <v>545742</v>
       </c>
-      <c r="D55" s="32">
+      <c r="D55" s="27">
         <v>43929</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55" s="27">
         <f t="shared" si="0"/>
         <v>43959</v>
       </c>
-      <c r="F55" s="32">
+      <c r="F55" s="27">
         <v>43941</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H55" s="31">
+      <c r="H55" s="26">
         <v>233209</v>
       </c>
-      <c r="I55" s="31" t="s">
+      <c r="I55" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J55" s="35">
+      <c r="J55" s="29">
         <v>1058.31</v>
       </c>
-      <c r="K55" s="32" t="str">
+      <c r="K55" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L55" s="34">
+      <c r="L55" s="26">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="M55" s="34">
+      <c r="M55" s="26">
         <f>IF(F55&gt;E55,NETWORKDAYS(E55,F55,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N55" s="33">
-        <f>J55*M55*Penalty_Rate</f>
+      <c r="N55" s="28">
+        <f>M55*(J55*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="31" t="s">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="26">
         <v>545743</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="27">
         <v>43921</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="27">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="27">
         <v>43929</v>
       </c>
-      <c r="G56" s="31" t="s">
+      <c r="G56" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="26">
         <v>222998</v>
       </c>
-      <c r="I56" s="31" t="s">
+      <c r="I56" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J56" s="35">
+      <c r="J56" s="29">
         <v>705.54</v>
       </c>
-      <c r="K56" s="32" t="str">
+      <c r="K56" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L56" s="34">
+      <c r="L56" s="26">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="M56" s="34">
+      <c r="M56" s="26">
         <f>IF(F56&gt;E56,NETWORKDAYS(E56,F56,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N56" s="33">
-        <f>J56*M56*Penalty_Rate</f>
+      <c r="N56" s="28">
+        <f>M56*(J56*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="31" t="s">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="B57" s="31" t="s">
+      <c r="B57" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="26">
         <v>545745</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="27">
         <v>43935</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="27">
         <f t="shared" si="0"/>
         <v>43965</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="27">
         <v>43948</v>
       </c>
-      <c r="G57" s="31" t="s">
+      <c r="G57" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="26">
         <v>228246</v>
       </c>
-      <c r="I57" s="31" t="s">
+      <c r="I57" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J57" s="35">
+      <c r="J57" s="29">
         <v>138.6</v>
       </c>
-      <c r="K57" s="32" t="str">
+      <c r="K57" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L57" s="34">
+      <c r="L57" s="26">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="M57" s="34">
+      <c r="M57" s="26">
         <f>IF(F57&gt;E57,NETWORKDAYS(E57,F57,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N57" s="33">
-        <f>J57*M57*Penalty_Rate</f>
+      <c r="N57" s="28">
+        <f>M57*(J57*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="31" t="s">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="B58" s="31" t="s">
+      <c r="B58" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="26">
         <v>545747</v>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="27">
         <v>43914</v>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="27">
         <f t="shared" si="0"/>
         <v>43945</v>
       </c>
-      <c r="F58" s="32">
+      <c r="F58" s="27">
         <v>43928</v>
       </c>
-      <c r="G58" s="31" t="s">
+      <c r="G58" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H58" s="31">
+      <c r="H58" s="26">
         <v>314876</v>
       </c>
-      <c r="I58" s="31" t="s">
+      <c r="I58" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J58" s="35">
+      <c r="J58" s="29">
         <v>417.12</v>
       </c>
-      <c r="K58" s="32" t="str">
+      <c r="K58" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L58" s="34">
+      <c r="L58" s="26">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="M58" s="34">
+      <c r="M58" s="26">
         <f>IF(F58&gt;E58,NETWORKDAYS(E58,F58,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N58" s="33">
-        <f>J58*M58*Penalty_Rate</f>
+      <c r="N58" s="28">
+        <f>M58*(J58*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="B59" s="31" t="s">
+      <c r="B59" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="26">
         <v>545748</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="27">
         <v>43913</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="27">
         <f t="shared" si="0"/>
         <v>43944</v>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="27">
         <v>43939</v>
       </c>
-      <c r="G59" s="31" t="s">
+      <c r="G59" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H59" s="31">
+      <c r="H59" s="26">
         <v>223602</v>
       </c>
-      <c r="I59" s="31" t="s">
+      <c r="I59" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J59" s="35">
+      <c r="J59" s="29">
         <v>422.73</v>
       </c>
-      <c r="K59" s="32" t="str">
+      <c r="K59" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="26">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="26">
         <f>IF(F59&gt;E59,NETWORKDAYS(E59,F59,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N59" s="33">
-        <f>J59*M59*Penalty_Rate</f>
+      <c r="N59" s="28">
+        <f>M59*(J59*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="31" t="s">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="B60" s="31" t="s">
+      <c r="B60" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="26">
         <v>545750</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="27">
         <v>43908</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="27">
         <f t="shared" si="0"/>
         <v>43941</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="27">
         <v>43935</v>
       </c>
-      <c r="G60" s="31" t="s">
+      <c r="G60" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="26">
         <v>319833</v>
       </c>
-      <c r="I60" s="31" t="s">
+      <c r="I60" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J60" s="35">
+      <c r="J60" s="29">
         <v>1061.94</v>
       </c>
-      <c r="K60" s="32" t="str">
+      <c r="K60" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L60" s="34">
+      <c r="L60" s="26">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="M60" s="34">
+      <c r="M60" s="26">
         <f>IF(F60&gt;E60,NETWORKDAYS(E60,F60,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N60" s="33">
-        <f>J60*M60*Penalty_Rate</f>
+      <c r="N60" s="28">
+        <f>M60*(J60*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="31" t="s">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="B61" s="31" t="s">
+      <c r="B61" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="26">
         <v>545751</v>
       </c>
-      <c r="D61" s="32">
+      <c r="D61" s="27">
         <v>43912</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="27">
         <f t="shared" si="0"/>
         <v>43943</v>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="27">
         <v>43927</v>
       </c>
-      <c r="G61" s="31" t="s">
+      <c r="G61" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H61" s="31">
+      <c r="H61" s="26">
         <v>310345</v>
       </c>
-      <c r="I61" s="31" t="s">
+      <c r="I61" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J61" s="35">
+      <c r="J61" s="29">
         <v>602.58000000000004</v>
       </c>
-      <c r="K61" s="32" t="str">
+      <c r="K61" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L61" s="34">
+      <c r="L61" s="26">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="M61" s="34">
+      <c r="M61" s="26">
         <f>IF(F61&gt;E61,NETWORKDAYS(E61,F61,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N61" s="33">
-        <f>J61*M61*Penalty_Rate</f>
+      <c r="N61" s="28">
+        <f>M61*(J61*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="31" t="s">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="B62" s="31" t="s">
+      <c r="B62" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="26">
         <v>545753</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="27">
         <v>43927</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="27">
         <f t="shared" si="0"/>
         <v>43957</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="27">
         <v>43951</v>
       </c>
-      <c r="G62" s="31" t="s">
+      <c r="G62" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="26">
         <v>317142</v>
       </c>
-      <c r="I62" s="31" t="s">
+      <c r="I62" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J62" s="35">
+      <c r="J62" s="29">
         <v>132.66</v>
       </c>
-      <c r="K62" s="32" t="str">
+      <c r="K62" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="26">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="26">
         <f>IF(F62&gt;E62,NETWORKDAYS(E62,F62,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N62" s="33">
-        <f>J62*M62*Penalty_Rate</f>
+      <c r="N62" s="28">
+        <f>M62*(J62*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="31" t="s">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="B63" s="31" t="s">
+      <c r="B63" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="26">
         <v>545754</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="27">
         <v>43896</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="27">
         <f t="shared" si="0"/>
         <v>43927</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="27">
         <v>43925</v>
       </c>
-      <c r="G63" s="31" t="s">
+      <c r="G63" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="26">
         <v>313747</v>
       </c>
-      <c r="I63" s="31" t="s">
+      <c r="I63" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J63" s="35">
+      <c r="J63" s="29">
         <v>56.43</v>
       </c>
-      <c r="K63" s="32" t="str">
+      <c r="K63" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L63" s="34">
+      <c r="L63" s="26">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="M63" s="34">
+      <c r="M63" s="26">
         <f>IF(F63&gt;E63,NETWORKDAYS(E63,F63,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N63" s="33">
-        <f>J63*M63*Penalty_Rate</f>
+      <c r="N63" s="28">
+        <f>M63*(J63*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="31" t="s">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="B64" s="31" t="s">
+      <c r="B64" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="26">
         <v>545756</v>
       </c>
-      <c r="D64" s="32">
+      <c r="D64" s="27">
         <v>43881</v>
       </c>
-      <c r="E64" s="32">
+      <c r="E64" s="27">
         <f t="shared" si="0"/>
         <v>43910</v>
       </c>
-      <c r="F64" s="32">
+      <c r="F64" s="27">
         <v>43926</v>
       </c>
-      <c r="G64" s="31" t="s">
+      <c r="G64" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H64" s="31">
+      <c r="H64" s="26">
         <v>234966</v>
       </c>
-      <c r="I64" s="31" t="s">
+      <c r="I64" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J64" s="35">
+      <c r="J64" s="29">
         <v>511.83</v>
       </c>
-      <c r="K64" s="32" t="str">
+      <c r="K64" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Feb</v>
       </c>
-      <c r="L64" s="34">
+      <c r="L64" s="26">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M64" s="34">
+      <c r="M64" s="26">
         <f>IF(F64&gt;E64,NETWORKDAYS(E64,F64,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>11</v>
       </c>
-      <c r="N64" s="33">
-        <f>J64*M64*Penalty_Rate</f>
-        <v>20.268467999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="31" t="s">
+      <c r="N64" s="28">
+        <f>M64*(J64*Penalty_Rate+flat_rate)</f>
+        <v>42.268467999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="B65" s="31" t="s">
+      <c r="B65" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="26">
         <v>545758</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="27">
         <v>43916</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="27">
         <f t="shared" si="0"/>
         <v>43948</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="27">
         <v>43929</v>
       </c>
-      <c r="G65" s="31" t="s">
+      <c r="G65" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="26">
         <v>215639</v>
       </c>
-      <c r="I65" s="31" t="s">
+      <c r="I65" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J65" s="35">
+      <c r="J65" s="29">
         <v>361.02</v>
       </c>
-      <c r="K65" s="32" t="str">
+      <c r="K65" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="26">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="26">
         <f>IF(F65&gt;E65,NETWORKDAYS(E65,F65,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N65" s="33">
-        <f>J65*M65*Penalty_Rate</f>
+      <c r="N65" s="28">
+        <f>M65*(J65*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="31" t="s">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="B66" s="31" t="s">
+      <c r="B66" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="26">
         <v>545760</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="27">
         <v>43932</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="27">
         <f t="shared" si="0"/>
         <v>43962</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="27">
         <v>43948</v>
       </c>
-      <c r="G66" s="31" t="s">
+      <c r="G66" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="26">
         <v>328536</v>
       </c>
-      <c r="I66" s="31" t="s">
+      <c r="I66" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J66" s="35">
+      <c r="J66" s="29">
         <v>668.25</v>
       </c>
-      <c r="K66" s="32" t="str">
+      <c r="K66" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Apr</v>
       </c>
-      <c r="L66" s="34">
+      <c r="L66" s="26">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="M66" s="34">
+      <c r="M66" s="26">
         <f>IF(F66&gt;E66,NETWORKDAYS(E66,F66,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N66" s="33">
-        <f>J66*M66*Penalty_Rate</f>
+      <c r="N66" s="28">
+        <f>M66*(J66*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="31" t="s">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="B67" s="31" t="s">
+      <c r="B67" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="26">
         <v>545762</v>
       </c>
-      <c r="D67" s="32">
+      <c r="D67" s="27">
         <v>43914</v>
       </c>
-      <c r="E67" s="32">
+      <c r="E67" s="27">
         <f t="shared" si="0"/>
         <v>43945</v>
       </c>
-      <c r="F67" s="32">
+      <c r="F67" s="27">
         <v>43933</v>
       </c>
-      <c r="G67" s="31" t="s">
+      <c r="G67" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H67" s="31">
+      <c r="H67" s="26">
         <v>210023</v>
       </c>
-      <c r="I67" s="31" t="s">
+      <c r="I67" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J67" s="35">
+      <c r="J67" s="29">
         <v>126.72</v>
       </c>
-      <c r="K67" s="32" t="str">
+      <c r="K67" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L67" s="34">
+      <c r="L67" s="26">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="M67" s="34">
+      <c r="M67" s="26">
         <f>IF(F67&gt;E67,NETWORKDAYS(E67,F67,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N67" s="33">
-        <f>J67*M67*Penalty_Rate</f>
+      <c r="N67" s="28">
+        <f>M67*(J67*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="31" t="s">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="B68" s="31" t="s">
+      <c r="B68" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="26">
         <v>545763</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="27">
         <v>43905</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="27">
         <f t="shared" si="0"/>
         <v>43936</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="27">
         <v>43943</v>
       </c>
-      <c r="G68" s="31" t="s">
+      <c r="G68" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="26">
         <v>338938</v>
       </c>
-      <c r="I68" s="31" t="s">
+      <c r="I68" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J68" s="35">
+      <c r="J68" s="29">
         <v>1000.23</v>
       </c>
-      <c r="K68" s="32" t="str">
+      <c r="K68" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L68" s="34">
+      <c r="L68" s="26">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="M68" s="34">
+      <c r="M68" s="26">
         <f>IF(F68&gt;E68,NETWORKDAYS(E68,F68,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>6</v>
       </c>
-      <c r="N68" s="33">
-        <f>J68*M68*Penalty_Rate</f>
-        <v>21.604968</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="31" t="s">
+      <c r="N68" s="28">
+        <f>M68*(J68*Penalty_Rate+flat_rate)</f>
+        <v>33.604968</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="B69" s="31" t="s">
+      <c r="B69" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="26">
         <v>545765</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="27">
         <v>43918</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="27">
         <f t="shared" si="0"/>
         <v>43949</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="27">
         <v>43939</v>
       </c>
-      <c r="G69" s="31" t="s">
+      <c r="G69" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="26">
         <v>320536</v>
       </c>
-      <c r="I69" s="31" t="s">
+      <c r="I69" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J69" s="35">
+      <c r="J69" s="29">
         <v>948.75</v>
       </c>
-      <c r="K69" s="32" t="str">
+      <c r="K69" s="27" t="str">
         <f t="shared" si="1"/>
         <v>Mar</v>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="26">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="26">
         <f>IF(F69&gt;E69,NETWORKDAYS(E69,F69,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N69" s="33">
-        <f>J69*M69*Penalty_Rate</f>
+      <c r="N69" s="28">
+        <f>M69*(J69*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="31" t="s">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="B70" s="31" t="s">
+      <c r="B70" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="26">
         <v>545767</v>
       </c>
-      <c r="D70" s="32">
+      <c r="D70" s="27">
         <v>43904</v>
       </c>
-      <c r="E70" s="32">
+      <c r="E70" s="27">
         <f t="shared" ref="E70:E88" si="3">WORKDAY(EDATE(D70,1)-1,1)</f>
         <v>43935</v>
       </c>
-      <c r="F70" s="32">
+      <c r="F70" s="27">
         <v>43937</v>
       </c>
-      <c r="G70" s="31" t="s">
+      <c r="G70" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H70" s="31">
+      <c r="H70" s="26">
         <v>322800</v>
       </c>
-      <c r="I70" s="31" t="s">
+      <c r="I70" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J70" s="35">
+      <c r="J70" s="29">
         <v>446.49</v>
       </c>
-      <c r="K70" s="32" t="str">
+      <c r="K70" s="27" t="str">
         <f t="shared" ref="K70:K88" si="4">TEXT(D70,"MMM")</f>
         <v>Mar</v>
       </c>
-      <c r="L70" s="34">
+      <c r="L70" s="26">
         <f t="shared" ref="L70:L88" si="5">DAY(D70)</f>
         <v>14</v>
       </c>
-      <c r="M70" s="34">
+      <c r="M70" s="26">
         <f>IF(F70&gt;E70,NETWORKDAYS(E70,F70,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>3</v>
       </c>
-      <c r="N70" s="33">
-        <f>J70*M70*Penalty_Rate</f>
-        <v>4.8220919999999996</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="31" t="s">
+      <c r="N70" s="28">
+        <f>M70*(J70*Penalty_Rate+flat_rate)</f>
+        <v>10.822092</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="B71" s="31" t="s">
+      <c r="B71" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="26">
         <v>545768</v>
       </c>
-      <c r="D71" s="32">
+      <c r="D71" s="27">
         <v>43933</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="27">
         <f t="shared" si="3"/>
         <v>43963</v>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="27">
         <v>43940</v>
       </c>
-      <c r="G71" s="31" t="s">
+      <c r="G71" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H71" s="31">
+      <c r="H71" s="26">
         <v>321358</v>
       </c>
-      <c r="I71" s="31" t="s">
+      <c r="I71" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J71" s="35">
+      <c r="J71" s="29">
         <v>242.22</v>
       </c>
-      <c r="K71" s="32" t="str">
+      <c r="K71" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Apr</v>
       </c>
-      <c r="L71" s="34">
+      <c r="L71" s="26">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="M71" s="34">
+      <c r="M71" s="26">
         <f>IF(F71&gt;E71,NETWORKDAYS(E71,F71,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N71" s="33">
-        <f>J71*M71*Penalty_Rate</f>
+      <c r="N71" s="28">
+        <f>M71*(J71*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="31" t="s">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="B72" s="31" t="s">
+      <c r="B72" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="26">
         <v>545769</v>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="27">
         <v>43887</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="27">
         <f t="shared" si="3"/>
         <v>43916</v>
       </c>
-      <c r="F72" s="32">
+      <c r="F72" s="27">
         <v>43929</v>
       </c>
-      <c r="G72" s="31" t="s">
+      <c r="G72" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H72" s="31">
+      <c r="H72" s="26">
         <v>316190</v>
       </c>
-      <c r="I72" s="31" t="s">
+      <c r="I72" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J72" s="35">
+      <c r="J72" s="29">
         <v>600.6</v>
       </c>
-      <c r="K72" s="32" t="str">
+      <c r="K72" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Feb</v>
       </c>
-      <c r="L72" s="34">
+      <c r="L72" s="26">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="M72" s="34">
+      <c r="M72" s="26">
         <f>IF(F72&gt;E72,NETWORKDAYS(E72,F72,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>10</v>
       </c>
-      <c r="N72" s="33">
-        <f>J72*M72*Penalty_Rate</f>
-        <v>21.621600000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="31" t="s">
+      <c r="N72" s="28">
+        <f>M72*(J72*Penalty_Rate+flat_rate)</f>
+        <v>41.621600000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="B73" s="31" t="s">
+      <c r="B73" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="26">
         <v>545770</v>
       </c>
-      <c r="D73" s="32">
+      <c r="D73" s="27">
         <v>43905</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73" s="27">
         <f t="shared" si="3"/>
         <v>43936</v>
       </c>
-      <c r="F73" s="32">
+      <c r="F73" s="27">
         <v>43942</v>
       </c>
-      <c r="G73" s="31" t="s">
+      <c r="G73" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H73" s="31">
+      <c r="H73" s="26">
         <v>327938</v>
       </c>
-      <c r="I73" s="31" t="s">
+      <c r="I73" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J73" s="35">
+      <c r="J73" s="29">
         <v>546.80999999999995</v>
       </c>
-      <c r="K73" s="32" t="str">
+      <c r="K73" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L73" s="34">
+      <c r="L73" s="26">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="M73" s="34">
+      <c r="M73" s="26">
         <f>IF(F73&gt;E73,NETWORKDAYS(E73,F73,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>5</v>
       </c>
-      <c r="N73" s="33">
-        <f>J73*M73*Penalty_Rate</f>
-        <v>9.8425799999999981</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="31" t="s">
+      <c r="N73" s="28">
+        <f>M73*(J73*Penalty_Rate+flat_rate)</f>
+        <v>19.842579999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="B74" s="31" t="s">
+      <c r="B74" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="26">
         <v>545772</v>
       </c>
-      <c r="D74" s="32">
+      <c r="D74" s="27">
         <v>43900</v>
       </c>
-      <c r="E74" s="32">
+      <c r="E74" s="27">
         <f t="shared" si="3"/>
         <v>43931</v>
       </c>
-      <c r="F74" s="32">
+      <c r="F74" s="27">
         <v>43931</v>
       </c>
-      <c r="G74" s="31" t="s">
+      <c r="G74" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H74" s="31">
+      <c r="H74" s="26">
         <v>234487</v>
       </c>
-      <c r="I74" s="31" t="s">
+      <c r="I74" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J74" s="35">
+      <c r="J74" s="29">
         <v>840.51</v>
       </c>
-      <c r="K74" s="32" t="str">
+      <c r="K74" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L74" s="34">
+      <c r="L74" s="26">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="M74" s="34">
+      <c r="M74" s="26">
         <f>IF(F74&gt;E74,NETWORKDAYS(E74,F74,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N74" s="33">
-        <f>J74*M74*Penalty_Rate</f>
+      <c r="N74" s="28">
+        <f>M74*(J74*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="31" t="s">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="B75" s="31" t="s">
+      <c r="B75" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="26">
         <v>545773</v>
       </c>
-      <c r="D75" s="32">
+      <c r="D75" s="27">
         <v>43923</v>
       </c>
-      <c r="E75" s="32">
+      <c r="E75" s="27">
         <f t="shared" si="3"/>
         <v>43955</v>
       </c>
-      <c r="F75" s="32">
+      <c r="F75" s="27">
         <v>43951</v>
       </c>
-      <c r="G75" s="31" t="s">
+      <c r="G75" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H75" s="31">
+      <c r="H75" s="26">
         <v>231274</v>
       </c>
-      <c r="I75" s="31" t="s">
+      <c r="I75" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J75" s="35">
+      <c r="J75" s="29">
         <v>603.57000000000005</v>
       </c>
-      <c r="K75" s="32" t="str">
+      <c r="K75" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Apr</v>
       </c>
-      <c r="L75" s="34">
+      <c r="L75" s="26">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="M75" s="34">
+      <c r="M75" s="26">
         <f>IF(F75&gt;E75,NETWORKDAYS(E75,F75,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N75" s="33">
-        <f>J75*M75*Penalty_Rate</f>
+      <c r="N75" s="28">
+        <f>M75*(J75*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="31" t="s">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="B76" s="31" t="s">
+      <c r="B76" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="26">
         <v>545774</v>
       </c>
-      <c r="D76" s="32">
+      <c r="D76" s="27">
         <v>43914</v>
       </c>
-      <c r="E76" s="32">
+      <c r="E76" s="27">
         <f t="shared" si="3"/>
         <v>43945</v>
       </c>
-      <c r="F76" s="32">
+      <c r="F76" s="27">
         <v>43944</v>
       </c>
-      <c r="G76" s="31" t="s">
+      <c r="G76" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H76" s="31">
+      <c r="H76" s="26">
         <v>224955</v>
       </c>
-      <c r="I76" s="31" t="s">
+      <c r="I76" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J76" s="35">
+      <c r="J76" s="29">
         <v>816.75</v>
       </c>
-      <c r="K76" s="32" t="str">
+      <c r="K76" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L76" s="34">
+      <c r="L76" s="26">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="M76" s="34">
+      <c r="M76" s="26">
         <f>IF(F76&gt;E76,NETWORKDAYS(E76,F76,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N76" s="33">
-        <f>J76*M76*Penalty_Rate</f>
+      <c r="N76" s="28">
+        <f>M76*(J76*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="31" t="s">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="B77" s="31" t="s">
+      <c r="B77" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C77" s="31">
+      <c r="C77" s="26">
         <v>545775</v>
       </c>
-      <c r="D77" s="32">
+      <c r="D77" s="27">
         <v>43912</v>
       </c>
-      <c r="E77" s="32">
+      <c r="E77" s="27">
         <f t="shared" si="3"/>
         <v>43943</v>
       </c>
-      <c r="F77" s="32">
+      <c r="F77" s="27">
         <v>43951</v>
       </c>
-      <c r="G77" s="31" t="s">
+      <c r="G77" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H77" s="31">
+      <c r="H77" s="26">
         <v>217275</v>
       </c>
-      <c r="I77" s="31" t="s">
+      <c r="I77" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J77" s="35">
+      <c r="J77" s="29">
         <v>1065.57</v>
       </c>
-      <c r="K77" s="32" t="str">
+      <c r="K77" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L77" s="34">
+      <c r="L77" s="26">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="M77" s="34">
+      <c r="M77" s="26">
         <f>IF(F77&gt;E77,NETWORKDAYS(E77,F77,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>7</v>
       </c>
-      <c r="N77" s="33">
-        <f>J77*M77*Penalty_Rate</f>
-        <v>26.852363999999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="31" t="s">
+      <c r="N77" s="28">
+        <f>M77*(J77*Penalty_Rate+flat_rate)</f>
+        <v>40.852363999999994</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="B78" s="31" t="s">
+      <c r="B78" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C78" s="31">
+      <c r="C78" s="26">
         <v>545776</v>
       </c>
-      <c r="D78" s="32">
+      <c r="D78" s="27">
         <v>43919</v>
       </c>
-      <c r="E78" s="32">
+      <c r="E78" s="27">
         <f t="shared" si="3"/>
         <v>43950</v>
       </c>
-      <c r="F78" s="32">
+      <c r="F78" s="27">
         <v>43925</v>
       </c>
-      <c r="G78" s="31" t="s">
+      <c r="G78" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H78" s="31">
+      <c r="H78" s="26">
         <v>226240</v>
       </c>
-      <c r="I78" s="31" t="s">
+      <c r="I78" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J78" s="35">
+      <c r="J78" s="29">
         <v>523.38</v>
       </c>
-      <c r="K78" s="32" t="str">
+      <c r="K78" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L78" s="34">
+      <c r="L78" s="26">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="M78" s="34">
+      <c r="M78" s="26">
         <f>IF(F78&gt;E78,NETWORKDAYS(E78,F78,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N78" s="33">
-        <f>J78*M78*Penalty_Rate</f>
+      <c r="N78" s="28">
+        <f>M78*(J78*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="31" t="s">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="B79" s="31" t="s">
+      <c r="B79" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C79" s="31">
+      <c r="C79" s="26">
         <v>545778</v>
       </c>
-      <c r="D79" s="32">
+      <c r="D79" s="27">
         <v>43890</v>
       </c>
-      <c r="E79" s="32">
+      <c r="E79" s="27">
         <f t="shared" si="3"/>
         <v>43920</v>
       </c>
-      <c r="F79" s="32">
+      <c r="F79" s="27">
         <v>43932</v>
       </c>
-      <c r="G79" s="31" t="s">
+      <c r="G79" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H79" s="31">
+      <c r="H79" s="26">
         <v>325643</v>
       </c>
-      <c r="I79" s="31" t="s">
+      <c r="I79" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J79" s="35">
+      <c r="J79" s="29">
         <v>650.42999999999995</v>
       </c>
-      <c r="K79" s="32" t="str">
+      <c r="K79" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Feb</v>
       </c>
-      <c r="L79" s="34">
+      <c r="L79" s="26">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="M79" s="34">
+      <c r="M79" s="26">
         <f>IF(F79&gt;E79,NETWORKDAYS(E79,F79,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>9</v>
       </c>
-      <c r="N79" s="33">
-        <f>J79*M79*Penalty_Rate</f>
-        <v>21.073931999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="31" t="s">
+      <c r="N79" s="28">
+        <f>M79*(J79*Penalty_Rate+flat_rate)</f>
+        <v>39.073931999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="B80" s="31" t="s">
+      <c r="B80" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C80" s="31">
+      <c r="C80" s="26">
         <v>545780</v>
       </c>
-      <c r="D80" s="32">
+      <c r="D80" s="27">
         <v>43934</v>
       </c>
-      <c r="E80" s="32">
+      <c r="E80" s="27">
         <f t="shared" si="3"/>
         <v>43964</v>
       </c>
-      <c r="F80" s="32">
+      <c r="F80" s="27">
         <v>43943</v>
       </c>
-      <c r="G80" s="31" t="s">
+      <c r="G80" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H80" s="31">
+      <c r="H80" s="26">
         <v>312800</v>
       </c>
-      <c r="I80" s="31" t="s">
+      <c r="I80" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J80" s="35">
+      <c r="J80" s="29">
         <v>809.49</v>
       </c>
-      <c r="K80" s="32" t="str">
+      <c r="K80" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Apr</v>
       </c>
-      <c r="L80" s="34">
+      <c r="L80" s="26">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="M80" s="34">
+      <c r="M80" s="26">
         <f>IF(F80&gt;E80,NETWORKDAYS(E80,F80,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N80" s="33">
-        <f>J80*M80*Penalty_Rate</f>
+      <c r="N80" s="28">
+        <f>M80*(J80*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="31" t="s">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="B81" s="31" t="s">
+      <c r="B81" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C81" s="31">
+      <c r="C81" s="26">
         <v>545781</v>
       </c>
-      <c r="D81" s="32">
+      <c r="D81" s="27">
         <v>43901</v>
       </c>
-      <c r="E81" s="32">
+      <c r="E81" s="27">
         <f t="shared" si="3"/>
         <v>43934</v>
       </c>
-      <c r="F81" s="32">
+      <c r="F81" s="27">
         <v>43943</v>
       </c>
-      <c r="G81" s="31" t="s">
+      <c r="G81" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H81" s="31">
+      <c r="H81" s="26">
         <v>338807</v>
       </c>
-      <c r="I81" s="31" t="s">
+      <c r="I81" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J81" s="35">
+      <c r="J81" s="29">
         <v>424.38</v>
       </c>
-      <c r="K81" s="32" t="str">
+      <c r="K81" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L81" s="34">
+      <c r="L81" s="26">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="M81" s="34">
+      <c r="M81" s="26">
         <f>IF(F81&gt;E81,NETWORKDAYS(E81,F81,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>7</v>
       </c>
-      <c r="N81" s="33">
-        <f>J81*M81*Penalty_Rate</f>
-        <v>10.694375999999998</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="31" t="s">
+      <c r="N81" s="28">
+        <f>M81*(J81*Penalty_Rate+flat_rate)</f>
+        <v>24.694375999999998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="B82" s="31" t="s">
+      <c r="B82" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C82" s="26">
         <v>545783</v>
       </c>
-      <c r="D82" s="32">
+      <c r="D82" s="27">
         <v>43933</v>
       </c>
-      <c r="E82" s="32">
+      <c r="E82" s="27">
         <f t="shared" si="3"/>
         <v>43963</v>
       </c>
-      <c r="F82" s="32">
+      <c r="F82" s="27">
         <v>43935</v>
       </c>
-      <c r="G82" s="31" t="s">
+      <c r="G82" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H82" s="31">
+      <c r="H82" s="26">
         <v>239476</v>
       </c>
-      <c r="I82" s="31" t="s">
+      <c r="I82" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J82" s="35">
+      <c r="J82" s="29">
         <v>955.68</v>
       </c>
-      <c r="K82" s="32" t="str">
+      <c r="K82" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Apr</v>
       </c>
-      <c r="L82" s="34">
+      <c r="L82" s="26">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="M82" s="34">
+      <c r="M82" s="26">
         <f>IF(F82&gt;E82,NETWORKDAYS(E82,F82,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N82" s="33">
-        <f>J82*M82*Penalty_Rate</f>
+      <c r="N82" s="28">
+        <f>M82*(J82*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="31" t="s">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="26" t="s">
         <v>330</v>
       </c>
-      <c r="B83" s="31" t="s">
+      <c r="B83" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C83" s="26">
         <v>545784</v>
       </c>
-      <c r="D83" s="32">
+      <c r="D83" s="27">
         <v>43942</v>
       </c>
-      <c r="E83" s="32">
+      <c r="E83" s="27">
         <f t="shared" si="3"/>
         <v>43972</v>
       </c>
-      <c r="F83" s="32">
+      <c r="F83" s="27">
         <v>43950</v>
       </c>
-      <c r="G83" s="31" t="s">
+      <c r="G83" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H83" s="31">
+      <c r="H83" s="26">
         <v>213693</v>
       </c>
-      <c r="I83" s="31" t="s">
+      <c r="I83" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J83" s="35">
+      <c r="J83" s="29">
         <v>764.28</v>
       </c>
-      <c r="K83" s="32" t="str">
+      <c r="K83" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Apr</v>
       </c>
-      <c r="L83" s="34">
+      <c r="L83" s="26">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="M83" s="34">
+      <c r="M83" s="26">
         <f>IF(F83&gt;E83,NETWORKDAYS(E83,F83,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N83" s="33">
-        <f>J83*M83*Penalty_Rate</f>
+      <c r="N83" s="28">
+        <f>M83*(J83*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="31" t="s">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="B84" s="31" t="s">
+      <c r="B84" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="26">
         <v>545785</v>
       </c>
-      <c r="D84" s="32">
+      <c r="D84" s="27">
         <v>43897</v>
       </c>
-      <c r="E84" s="32">
+      <c r="E84" s="27">
         <f t="shared" si="3"/>
         <v>43928</v>
       </c>
-      <c r="F84" s="32">
+      <c r="F84" s="27">
         <v>43926</v>
       </c>
-      <c r="G84" s="31" t="s">
+      <c r="G84" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H84" s="31">
+      <c r="H84" s="26">
         <v>235040</v>
       </c>
-      <c r="I84" s="31" t="s">
+      <c r="I84" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J84" s="35">
+      <c r="J84" s="29">
         <v>335.61</v>
       </c>
-      <c r="K84" s="32" t="str">
+      <c r="K84" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L84" s="34">
+      <c r="L84" s="26">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="M84" s="34">
+      <c r="M84" s="26">
         <f>IF(F84&gt;E84,NETWORKDAYS(E84,F84,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N84" s="33">
-        <f>J84*M84*Penalty_Rate</f>
+      <c r="N84" s="28">
+        <f>M84*(J84*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="31" t="s">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="B85" s="31" t="s">
+      <c r="B85" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C85" s="26">
         <v>545786</v>
       </c>
-      <c r="D85" s="32">
+      <c r="D85" s="27">
         <v>43898</v>
       </c>
-      <c r="E85" s="32">
+      <c r="E85" s="27">
         <f t="shared" si="3"/>
         <v>43929</v>
       </c>
-      <c r="F85" s="32">
+      <c r="F85" s="27">
         <v>43940</v>
       </c>
-      <c r="G85" s="31" t="s">
+      <c r="G85" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H85" s="31">
+      <c r="H85" s="26">
         <v>211771</v>
       </c>
-      <c r="I85" s="31" t="s">
+      <c r="I85" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J85" s="35">
+      <c r="J85" s="29">
         <v>763.29</v>
       </c>
-      <c r="K85" s="32" t="str">
+      <c r="K85" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L85" s="34">
+      <c r="L85" s="26">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="M85" s="34">
+      <c r="M85" s="26">
         <f>IF(F85&gt;E85,NETWORKDAYS(E85,F85,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>6</v>
       </c>
-      <c r="N85" s="33">
-        <f>J85*M85*Penalty_Rate</f>
-        <v>16.487064</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="31" t="s">
+      <c r="N85" s="28">
+        <f>M85*(J85*Penalty_Rate+flat_rate)</f>
+        <v>28.487063999999997</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="B86" s="31" t="s">
+      <c r="B86" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C86" s="26">
         <v>545788</v>
       </c>
-      <c r="D86" s="32">
+      <c r="D86" s="27">
         <v>43919</v>
       </c>
-      <c r="E86" s="32">
+      <c r="E86" s="27">
         <f t="shared" si="3"/>
         <v>43950</v>
       </c>
-      <c r="F86" s="32">
+      <c r="F86" s="27">
         <v>43933</v>
       </c>
-      <c r="G86" s="31" t="s">
+      <c r="G86" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H86" s="31">
+      <c r="H86" s="26">
         <v>326543</v>
       </c>
-      <c r="I86" s="31" t="s">
+      <c r="I86" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J86" s="35">
+      <c r="J86" s="29">
         <v>446.16</v>
       </c>
-      <c r="K86" s="32" t="str">
+      <c r="K86" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L86" s="34">
+      <c r="L86" s="26">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="M86" s="34">
+      <c r="M86" s="26">
         <f>IF(F86&gt;E86,NETWORKDAYS(E86,F86,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N86" s="33">
-        <f>J86*M86*Penalty_Rate</f>
+      <c r="N86" s="28">
+        <f>M86*(J86*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="31" t="s">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="B87" s="31" t="s">
+      <c r="B87" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C87" s="26">
         <v>545789</v>
       </c>
-      <c r="D87" s="32">
+      <c r="D87" s="27">
         <v>43898</v>
       </c>
-      <c r="E87" s="32">
+      <c r="E87" s="27">
         <f t="shared" si="3"/>
         <v>43929</v>
       </c>
-      <c r="F87" s="32">
+      <c r="F87" s="27">
         <v>43941</v>
       </c>
-      <c r="G87" s="31" t="s">
+      <c r="G87" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H87" s="31">
+      <c r="H87" s="26">
         <v>338553</v>
       </c>
-      <c r="I87" s="31" t="s">
+      <c r="I87" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J87" s="35">
+      <c r="J87" s="29">
         <v>1032.24</v>
       </c>
-      <c r="K87" s="32" t="str">
+      <c r="K87" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L87" s="34">
+      <c r="L87" s="26">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="M87" s="34">
+      <c r="M87" s="26">
         <f>IF(F87&gt;E87,NETWORKDAYS(E87,F87,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>7</v>
       </c>
-      <c r="N87" s="33">
-        <f>J87*M87*Penalty_Rate</f>
-        <v>26.012447999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="31" t="s">
+      <c r="N87" s="28">
+        <f>M87*(J87*Penalty_Rate+flat_rate)</f>
+        <v>40.012447999999992</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="B88" s="31" t="s">
+      <c r="B88" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="26">
         <v>545790</v>
       </c>
-      <c r="D88" s="32">
+      <c r="D88" s="27">
         <v>43915</v>
       </c>
-      <c r="E88" s="32">
+      <c r="E88" s="27">
         <f t="shared" si="3"/>
         <v>43948</v>
       </c>
-      <c r="F88" s="32">
+      <c r="F88" s="27">
         <v>43933</v>
       </c>
-      <c r="G88" s="31" t="s">
+      <c r="G88" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H88" s="31">
+      <c r="H88" s="26">
         <v>213342</v>
       </c>
-      <c r="I88" s="31" t="s">
+      <c r="I88" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="J88" s="35">
+      <c r="J88" s="29">
         <v>533.28</v>
       </c>
-      <c r="K88" s="32" t="str">
+      <c r="K88" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Mar</v>
       </c>
-      <c r="L88" s="34">
+      <c r="L88" s="26">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="M88" s="34">
+      <c r="M88" s="26">
         <f>IF(F88&gt;E88,NETWORKDAYS(E88,F88,'NSW Holidays 2020'!$A$4:$A$15),0)</f>
         <v>0</v>
       </c>
-      <c r="N88" s="33">
-        <f>J88*M88*Penalty_Rate</f>
+      <c r="N88" s="28">
+        <f>M88*(J88*Penalty_Rate+flat_rate)</f>
         <v>0</v>
       </c>
     </row>
@@ -11859,66 +11844,86 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB51EA9-9779-45DC-8275-7C6ACC2F16A5}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="3" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <f>SUM('Supplier Invoice Statement'!Q2:Q85)</f>
+        <v>48282.62999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>397</v>
       </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
+        <f>SUM(Amount_Paid)</f>
+        <v>45711.929999999993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>348</v>
       </c>
       <c r="B5" s="3">
         <f>B3-B4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2570.6999999999971</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>251</v>
       </c>
-      <c r="C8" s="12"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f>COUNTIFS(Location,A8)</f>
+        <v>40</v>
+      </c>
+      <c r="C8" s="11">
+        <f>SUMIFS(Amount_Paid,Location,A8)</f>
+        <v>24082.739999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>253</v>
       </c>
-      <c r="C9" s="12"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C10" s="12"/>
+      <c r="B9">
+        <f>COUNTIFS(Location,A9)</f>
+        <v>44</v>
+      </c>
+      <c r="C9" s="11">
+        <f>SUMIFS(Amount_Paid,Location,A9)</f>
+        <v>21629.190000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C10" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11928,34 +11933,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2BD081-91A7-4DE1-81D8-87D0B9859C69}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="9" style="7"/>
-    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:3" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="25" t="s">
         <v>376</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="23" t="s">
         <v>362</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="24" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="21">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="20">
         <v>43831</v>
       </c>
       <c r="B4" s="7" t="str">
@@ -11966,8 +11971,8 @@
         <v>364</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="21">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
         <v>43857</v>
       </c>
       <c r="B5" s="7" t="str">
@@ -11978,8 +11983,8 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="20">
         <v>43931</v>
       </c>
       <c r="B6" s="7" t="str">
@@ -11990,8 +11995,8 @@
         <v>367</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="20">
         <v>43932</v>
       </c>
       <c r="B7" s="7" t="str">
@@ -12002,8 +12007,8 @@
         <v>368</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="20">
         <v>43933</v>
       </c>
       <c r="B8" s="7" t="str">
@@ -12014,8 +12019,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
         <v>43934</v>
       </c>
       <c r="B9" s="7" t="str">
@@ -12026,8 +12031,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="20">
         <v>43946</v>
       </c>
       <c r="B10" s="7" t="str">
@@ -12038,8 +12043,8 @@
         <v>371</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="20">
         <v>43990</v>
       </c>
       <c r="B11" s="7" t="str">
@@ -12050,8 +12055,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="20">
         <v>44109</v>
       </c>
       <c r="B12" s="7" t="str">
@@ -12062,8 +12067,8 @@
         <v>366</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="20">
         <v>44190</v>
       </c>
       <c r="B13" s="7" t="str">
@@ -12074,8 +12079,8 @@
         <v>373</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="20">
         <v>44191</v>
       </c>
       <c r="B14" s="7" t="str">
@@ -12086,8 +12091,8 @@
         <v>374</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="21">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="20">
         <v>44193</v>
       </c>
       <c r="B15" s="7" t="str">
@@ -12098,22 +12103,22 @@
         <v>375</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>392</v>
       </c>
       <c r="B19"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="24" t="s">
         <v>393</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="24" t="s">
         <v>394</v>
       </c>
-      <c r="C20" s="27"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="24"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>377</v>
       </c>
@@ -12121,7 +12126,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -12129,7 +12134,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
@@ -12137,7 +12142,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>4</v>
       </c>
@@ -12145,7 +12150,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>5</v>
       </c>
@@ -12153,7 +12158,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -12161,7 +12166,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>7</v>
       </c>
@@ -12169,7 +12174,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>11</v>
       </c>
@@ -12177,7 +12182,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>12</v>
       </c>
@@ -12185,7 +12190,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>13</v>
       </c>
@@ -12193,7 +12198,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>14</v>
       </c>
@@ -12201,7 +12206,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>15</v>
       </c>
@@ -12209,7 +12214,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>16</v>
       </c>
@@ -12217,7 +12222,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>17</v>
       </c>
@@ -12225,8 +12230,8 @@
         <v>391</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
         <v>395</v>
       </c>
     </row>
